--- a/tests/traces/compare_test_e2e/reference/mi300_perf_report.xlsx
+++ b/tests/traces/compare_test_e2e/reference/mi300_perf_report.xlsx
@@ -1,24 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SDPA_fwd" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UnaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BinaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kernel_summary" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="short_kernel_histogram" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="short_kernels_summary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="SDPA_fwd" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="UnaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="BinaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -565,3631 +562,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K49"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Parent op category</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Parent cpu_op</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel stream</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel duration (µs)_sum</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel duration (µs)_count</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel duration (µs)_mean</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel duration (µs)_min</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel duration (µs)_max</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Percent of kernels time (%)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Percent of total time (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>GEMM</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>aten::mm</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x224x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_7_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>5308.273</v>
-      </c>
-      <c r="F2" t="n">
-        <v>48</v>
-      </c>
-      <c r="G2" t="n">
-        <v>110.5890208333333</v>
-      </c>
-      <c r="H2" t="n">
-        <v>105</v>
-      </c>
-      <c r="I2" t="n">
-        <v>118.551</v>
-      </c>
-      <c r="J2" t="n">
-        <v>12.32703502541751</v>
-      </c>
-      <c r="K2" t="n">
-        <v>16.02191170671068</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>aten::_flash_attention_forward</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>attn_fwd</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3908.798</v>
-      </c>
-      <c r="F3" t="n">
-        <v>24</v>
-      </c>
-      <c r="G3" t="n">
-        <v>162.8665833333333</v>
-      </c>
-      <c r="H3" t="n">
-        <v>138.557</v>
-      </c>
-      <c r="I3" t="n">
-        <v>173.077</v>
-      </c>
-      <c r="J3" t="n">
-        <v>9.07713108449432</v>
-      </c>
-      <c r="K3" t="n">
-        <v>11.79788915064603</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>GEMM</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>aten::mm</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3355.344</v>
-      </c>
-      <c r="F4" t="n">
-        <v>48</v>
-      </c>
-      <c r="G4" t="n">
-        <v>69.90300000000001</v>
-      </c>
-      <c r="H4" t="n">
-        <v>39.209</v>
-      </c>
-      <c r="I4" t="n">
-        <v>105.883</v>
-      </c>
-      <c r="J4" t="n">
-        <v>7.791883162438047</v>
-      </c>
-      <c r="K4" t="n">
-        <v>10.12740401890435</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>GEMM</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>aten::addmm</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2954.763</v>
-      </c>
-      <c r="F5" t="n">
-        <v>72</v>
-      </c>
-      <c r="G5" t="n">
-        <v>41.038375</v>
-      </c>
-      <c r="H5" t="n">
-        <v>39.57</v>
-      </c>
-      <c r="I5" t="n">
-        <v>45.023</v>
-      </c>
-      <c r="J5" t="n">
-        <v>6.861641628606464</v>
-      </c>
-      <c r="K5" t="n">
-        <v>8.918334060862271</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2787.634</v>
-      </c>
-      <c r="F6" t="n">
-        <v>52</v>
-      </c>
-      <c r="G6" t="n">
-        <v>53.60834615384616</v>
-      </c>
-      <c r="H6" t="n">
-        <v>39.811</v>
-      </c>
-      <c r="I6" t="n">
-        <v>102.314</v>
-      </c>
-      <c r="J6" t="n">
-        <v>6.473529518177516</v>
-      </c>
-      <c r="K6" t="n">
-        <v>8.41389013312328</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>aten::mul</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1})</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2470.609</v>
-      </c>
-      <c r="F7" t="n">
-        <v>145</v>
-      </c>
-      <c r="G7" t="n">
-        <v>17.03868275862069</v>
-      </c>
-      <c r="H7" t="n">
-        <v>13.029</v>
-      </c>
-      <c r="I7" t="n">
-        <v>22.731</v>
-      </c>
-      <c r="J7" t="n">
-        <v>5.737324300598657</v>
-      </c>
-      <c r="K7" t="n">
-        <v>7.457016483478668</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x224x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_7_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2454.377</v>
-      </c>
-      <c r="F8" t="n">
-        <v>22</v>
-      </c>
-      <c r="G8" t="n">
-        <v>111.5625909090909</v>
-      </c>
-      <c r="H8" t="n">
-        <v>106.965</v>
-      </c>
-      <c r="I8" t="n">
-        <v>118.03</v>
-      </c>
-      <c r="J8" t="n">
-        <v>5.699629850344765</v>
-      </c>
-      <c r="K8" t="n">
-        <v>7.408023586763798</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>attn_fwd</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1786.574</v>
-      </c>
-      <c r="F9" t="n">
-        <v>11</v>
-      </c>
-      <c r="G9" t="n">
-        <v>162.4158181818182</v>
-      </c>
-      <c r="H9" t="n">
-        <v>155.116</v>
-      </c>
-      <c r="I9" t="n">
-        <v>167.103</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.148837159185344</v>
-      </c>
-      <c r="K9" t="n">
-        <v>5.39239991716796</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>aten::copy_</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1447.588</v>
-      </c>
-      <c r="F10" t="n">
-        <v>96</v>
-      </c>
-      <c r="G10" t="n">
-        <v>15.07904166666667</v>
-      </c>
-      <c r="H10" t="n">
-        <v>12.988</v>
-      </c>
-      <c r="I10" t="n">
-        <v>16.276</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.361633431131761</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4.369241582656712</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>aten::cat</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 4, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1349.738</v>
-      </c>
-      <c r="F11" t="n">
-        <v>48</v>
-      </c>
-      <c r="G11" t="n">
-        <v>28.11954166666667</v>
-      </c>
-      <c r="H11" t="n">
-        <v>26.82</v>
-      </c>
-      <c r="I11" t="n">
-        <v>30.348</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.134403147904598</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4.073901825168423</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>aten::mul</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1})</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1154.164</v>
-      </c>
-      <c r="F12" t="n">
-        <v>49</v>
-      </c>
-      <c r="G12" t="n">
-        <v>23.55436734693878</v>
-      </c>
-      <c r="H12" t="n">
-        <v>18.441</v>
-      </c>
-      <c r="I12" t="n">
-        <v>27.221</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.680235182530359</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.483602614836129</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1})</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1060.415</v>
-      </c>
-      <c r="F13" t="n">
-        <v>63</v>
-      </c>
-      <c r="G13" t="n">
-        <v>16.83198412698412</v>
-      </c>
-      <c r="H13" t="n">
-        <v>14.072</v>
-      </c>
-      <c r="I13" t="n">
-        <v>21.007</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.462528367790826</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.200640868032145</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>aten::copy_</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1})</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1058.546</v>
-      </c>
-      <c r="F14" t="n">
-        <v>50</v>
-      </c>
-      <c r="G14" t="n">
-        <v>21.17092</v>
-      </c>
-      <c r="H14" t="n">
-        <v>3.086</v>
-      </c>
-      <c r="I14" t="n">
-        <v>23.012</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.458188118436186</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.194999682475216</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>aten::add</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>982.889</v>
-      </c>
-      <c r="F15" t="n">
-        <v>48</v>
-      </c>
-      <c r="G15" t="n">
-        <v>20.47685416666667</v>
-      </c>
-      <c r="H15" t="n">
-        <v>18.802</v>
-      </c>
-      <c r="I15" t="n">
-        <v>23.132</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.282495103228035</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2.966644853325583</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>aten::pow</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::pow_tensor_scalar_kernel_impl&lt;float, float&gt;(at::TensorIteratorBase&amp;, float)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::pow_tensor_scalar_kernel_impl&lt;float, float&gt;(at::TensorIteratorBase&amp;, float)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>928.082</v>
-      </c>
-      <c r="F16" t="n">
-        <v>49</v>
-      </c>
-      <c r="G16" t="n">
-        <v>18.94044897959184</v>
-      </c>
-      <c r="H16" t="n">
-        <v>14.031</v>
-      </c>
-      <c r="I16" t="n">
-        <v>21.93</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2.155220600082086</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2.801221387933035</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>aten::mul</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>909.1</v>
-      </c>
-      <c r="F17" t="n">
-        <v>24</v>
-      </c>
-      <c r="G17" t="n">
-        <v>37.87916666666667</v>
-      </c>
-      <c r="H17" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="I17" t="n">
-        <v>42.497</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2.111140015143731</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2.743928191442052</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>aten::silu</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::(anonymous namespace)::silu_kernel(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#6}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::silu_kernel(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#6}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>777.643</v>
-      </c>
-      <c r="F18" t="n">
-        <v>24</v>
-      </c>
-      <c r="G18" t="n">
-        <v>32.40179166666667</v>
-      </c>
-      <c r="H18" t="n">
-        <v>31.471</v>
-      </c>
-      <c r="I18" t="n">
-        <v>35.08</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.805866521610842</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2.347152734107988</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>aten::add</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>689.413</v>
-      </c>
-      <c r="F19" t="n">
-        <v>48</v>
-      </c>
-      <c r="G19" t="n">
-        <v>14.36277083333333</v>
-      </c>
-      <c r="H19" t="n">
-        <v>13.63</v>
-      </c>
-      <c r="I19" t="n">
-        <v>16.718</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.600976098625327</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2.080848934381959</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>aten::copy_</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>684.561</v>
-      </c>
-      <c r="F20" t="n">
-        <v>51</v>
-      </c>
-      <c r="G20" t="n">
-        <v>13.42276470588235</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.522</v>
-      </c>
-      <c r="I20" t="n">
-        <v>15.715</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.58970863481114</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2.066204187286066</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>660.473</v>
-      </c>
-      <c r="F21" t="n">
-        <v>44</v>
-      </c>
-      <c r="G21" t="n">
-        <v>15.01075</v>
-      </c>
-      <c r="H21" t="n">
-        <v>14.231</v>
-      </c>
-      <c r="I21" t="n">
-        <v>15.595</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1.533770739436834</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1.993499597828958</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>reduce</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>aten::mean</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4, 4&gt; &gt;(at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4, 4&gt;)</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>619.053</v>
-      </c>
-      <c r="F22" t="n">
-        <v>49</v>
-      </c>
-      <c r="G22" t="n">
-        <v>12.63373469387755</v>
-      </c>
-      <c r="H22" t="n">
-        <v>8.016999999999999</v>
-      </c>
-      <c r="I22" t="n">
-        <v>13.871</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1.43758393993485</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1.868481991746537</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 4, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>578.466</v>
-      </c>
-      <c r="F23" t="n">
-        <v>21</v>
-      </c>
-      <c r="G23" t="n">
-        <v>27.546</v>
-      </c>
-      <c r="H23" t="n">
-        <v>26.299</v>
-      </c>
-      <c r="I23" t="n">
-        <v>28.785</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1.34333155868456</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1.745978621923571</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1})</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>522.699</v>
-      </c>
-      <c r="F24" t="n">
-        <v>22</v>
-      </c>
-      <c r="G24" t="n">
-        <v>23.75904545454545</v>
-      </c>
-      <c r="H24" t="n">
-        <v>21.889</v>
-      </c>
-      <c r="I24" t="n">
-        <v>27.061</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1.213827713976035</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1.577657597336453</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>aten::neg</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>517.1</v>
-      </c>
-      <c r="F25" t="n">
-        <v>48</v>
-      </c>
-      <c r="G25" t="n">
-        <v>10.77291666666667</v>
-      </c>
-      <c r="H25" t="n">
-        <v>8.379</v>
-      </c>
-      <c r="I25" t="n">
-        <v>11.907</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1.200825543758468</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1.560758186992284</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1})</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>473.709</v>
-      </c>
-      <c r="F26" t="n">
-        <v>22</v>
-      </c>
-      <c r="G26" t="n">
-        <v>21.53222727272727</v>
-      </c>
-      <c r="H26" t="n">
-        <v>20.286</v>
-      </c>
-      <c r="I26" t="n">
-        <v>22.932</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1.100061627360821</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1.429791529688508</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>431.33</v>
-      </c>
-      <c r="F27" t="n">
-        <v>21</v>
-      </c>
-      <c r="G27" t="n">
-        <v>20.53952380952381</v>
-      </c>
-      <c r="H27" t="n">
-        <v>19.444</v>
-      </c>
-      <c r="I27" t="n">
-        <v>22.13</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1.001647808527055</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1.301879382702343</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::pow_tensor_scalar_kernel_impl&lt;float, float&gt;(at::TensorIteratorBase&amp;, float)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::pow_tensor_scalar_kernel_impl&lt;float, float&gt;(at::TensorIteratorBase&amp;, float)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>420.704</v>
-      </c>
-      <c r="F28" t="n">
-        <v>22</v>
-      </c>
-      <c r="G28" t="n">
-        <v>19.12290909090909</v>
-      </c>
-      <c r="H28" t="n">
-        <v>18</v>
-      </c>
-      <c r="I28" t="n">
-        <v>20.766</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.9769717841062903</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1.269807024367437</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>409.688</v>
-      </c>
-      <c r="F29" t="n">
-        <v>11</v>
-      </c>
-      <c r="G29" t="n">
-        <v>37.24436363636364</v>
-      </c>
-      <c r="H29" t="n">
-        <v>35.079</v>
-      </c>
-      <c r="I29" t="n">
-        <v>40.933</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.9513900896757287</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1.236557532609736</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::(anonymous namespace)::silu_kernel(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#6}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::silu_kernel(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#6}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>355.729</v>
-      </c>
-      <c r="F30" t="n">
-        <v>11</v>
-      </c>
-      <c r="G30" t="n">
-        <v>32.339</v>
-      </c>
-      <c r="H30" t="n">
-        <v>31.712</v>
-      </c>
-      <c r="I30" t="n">
-        <v>33.356</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.8260848382433884</v>
-      </c>
-      <c r="K30" t="n">
-        <v>1.07369357783906</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>314.782</v>
-      </c>
-      <c r="F31" t="n">
-        <v>22</v>
-      </c>
-      <c r="G31" t="n">
-        <v>14.30827272727273</v>
-      </c>
-      <c r="H31" t="n">
-        <v>13.39</v>
-      </c>
-      <c r="I31" t="n">
-        <v>15.956</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.7309964539071323</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0.95010362331813</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
-        <v>304.801</v>
-      </c>
-      <c r="F32" t="n">
-        <v>22</v>
-      </c>
-      <c r="G32" t="n">
-        <v>13.85459090909091</v>
-      </c>
-      <c r="H32" t="n">
-        <v>12.628</v>
-      </c>
-      <c r="I32" t="n">
-        <v>15.475</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.7078182683487234</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0.9199780625670761</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4, 4&gt; &gt;(at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4, 4&gt;)</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="n">
-        <v>280.382</v>
-      </c>
-      <c r="F33" t="n">
-        <v>22</v>
-      </c>
-      <c r="G33" t="n">
-        <v>12.74463636363636</v>
-      </c>
-      <c r="H33" t="n">
-        <v>11.866</v>
-      </c>
-      <c r="I33" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.6511117145814869</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.8462744188460075</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>aten::add</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;float&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;float&gt;, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
-        <v>223.305</v>
-      </c>
-      <c r="F34" t="n">
-        <v>49</v>
-      </c>
-      <c r="G34" t="n">
-        <v>4.557244897959184</v>
-      </c>
-      <c r="H34" t="n">
-        <v>1.602</v>
-      </c>
-      <c r="I34" t="n">
-        <v>5.332</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.5185657475323627</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.6739994332746314</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="n">
-        <v>216.277</v>
-      </c>
-      <c r="F35" t="n">
-        <v>20</v>
-      </c>
-      <c r="G35" t="n">
-        <v>10.81385</v>
-      </c>
-      <c r="H35" t="n">
-        <v>10.102</v>
-      </c>
-      <c r="I35" t="n">
-        <v>11.385</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.5022451095096697</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0.6527868853377106</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>aten::rsqrt</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::rsqrt_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::rsqrt_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>215.446</v>
-      </c>
-      <c r="F36" t="n">
-        <v>49</v>
-      </c>
-      <c r="G36" t="n">
-        <v>4.396857142857143</v>
-      </c>
-      <c r="H36" t="n">
-        <v>1.723</v>
-      </c>
-      <c r="I36" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.5003153357195648</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.6502786856599102</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>aten::fill_</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;int&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;int&gt;, std::array&lt;char*, 1ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="n">
-        <v>107.545</v>
-      </c>
-      <c r="F37" t="n">
-        <v>24</v>
-      </c>
-      <c r="G37" t="n">
-        <v>4.481041666666667</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.681</v>
-      </c>
-      <c r="I37" t="n">
-        <v>5.411</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.249744310778388</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0.3246020870626284</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;float&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;float&gt;, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="n">
-        <v>106.581</v>
-      </c>
-      <c r="F38" t="n">
-        <v>22</v>
-      </c>
-      <c r="G38" t="n">
-        <v>4.844590909090909</v>
-      </c>
-      <c r="H38" t="n">
-        <v>4.329</v>
-      </c>
-      <c r="I38" t="n">
-        <v>5.451</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.2475056802926345</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0.3216924547047468</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::rsqrt_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::rsqrt_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="n">
-        <v>101.091</v>
-      </c>
-      <c r="F39" t="n">
-        <v>22</v>
-      </c>
-      <c r="G39" t="n">
-        <v>4.595045454545454</v>
-      </c>
-      <c r="H39" t="n">
-        <v>4.249</v>
-      </c>
-      <c r="I39" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.2347566332316521</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0.3051220380607947</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;int&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;int&gt;, std::array&lt;char*, 1ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="n">
-        <v>53.152</v>
-      </c>
-      <c r="F40" t="n">
-        <v>11</v>
-      </c>
-      <c r="G40" t="n">
-        <v>4.832</v>
-      </c>
-      <c r="H40" t="n">
-        <v>4.489</v>
-      </c>
-      <c r="I40" t="n">
-        <v>5.371</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.1234312111812998</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0.16042819407274</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>GEMM</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>aten::bmm</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Cijk_Ailk_Bljk_S_B_Bias_HA_S_SAV_UserArgs_MT16x16x128_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA2_GRVWB2_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB512_LBSPPM0_LPA16_LPB8_LPM0_LRVW4_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="n">
-        <v>27.342</v>
-      </c>
-      <c r="F41" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" t="n">
-        <v>27.342</v>
-      </c>
-      <c r="H41" t="n">
-        <v>27.342</v>
-      </c>
-      <c r="I41" t="n">
-        <v>27.342</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0.0634944343791221</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0.08252610781037134</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>aten::index_select</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2, true&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, unsigned int, long)</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" t="n">
-        <v>21.008</v>
-      </c>
-      <c r="F42" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" t="n">
-        <v>21.008</v>
-      </c>
-      <c r="H42" t="n">
-        <v>21.008</v>
-      </c>
-      <c r="I42" t="n">
-        <v>21.008</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0.04878542452770818</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0.06340825370785901</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>aten::mul</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="n">
-        <v>7.415</v>
-      </c>
-      <c r="F43" t="n">
-        <v>2</v>
-      </c>
-      <c r="G43" t="n">
-        <v>3.7075</v>
-      </c>
-      <c r="H43" t="n">
-        <v>3.607</v>
-      </c>
-      <c r="I43" t="n">
-        <v>3.808</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0.01721934134010645</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0.02238062648723222</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>aten::cat</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="n">
-        <v>6.333</v>
-      </c>
-      <c r="F44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" t="n">
-        <v>6.333</v>
-      </c>
-      <c r="H44" t="n">
-        <v>6.333</v>
-      </c>
-      <c r="I44" t="n">
-        <v>6.333</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0.01470668762061957</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0.01911483581168465</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>aten::eq</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="n">
-        <v>5.572</v>
-      </c>
-      <c r="F45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" t="n">
-        <v>5.572</v>
-      </c>
-      <c r="H45" t="n">
-        <v>5.572</v>
-      </c>
-      <c r="I45" t="n">
-        <v>5.572</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0.0129394699861191</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0.01681791649182171</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>aten::cos</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::cos_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::cos_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="F46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="H46" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="I46" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0.01089126242550226</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0.01415578398180973</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>elementwise</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>aten::sin</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::sin_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sin_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" t="n">
-        <v>4.249</v>
-      </c>
-      <c r="F47" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" t="n">
-        <v>4.249</v>
-      </c>
-      <c r="H47" t="n">
-        <v>4.249</v>
-      </c>
-      <c r="I47" t="n">
-        <v>4.249</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0.009867158645193833</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0.01282471772680374</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>reduce</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>aten::all</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;bool, at::native::func_wrapper_t&lt;bool, at::native::and_kernel_cuda(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, bool)#1}&gt;, unsigned int, bool, 4, 4&gt; &gt;(at::native::ReduceOp&lt;bool, at::native::func_wrapper_t&lt;bool, at::native::and_kernel_cuda(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, bool)#1}&gt;, unsigned int, bool, 4, 4&gt;)</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" t="n">
-        <v>2.325</v>
-      </c>
-      <c r="F48" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" t="n">
-        <v>2.325</v>
-      </c>
-      <c r="H48" t="n">
-        <v>2.325</v>
-      </c>
-      <c r="I48" t="n">
-        <v>2.325</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.005399186596864125</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0.007017526174351306</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>aten::arange</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" t="n">
-        <v>2.284</v>
-      </c>
-      <c r="F49" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" t="n">
-        <v>2.284</v>
-      </c>
-      <c r="H49" t="n">
-        <v>2.284</v>
-      </c>
-      <c r="I49" t="n">
-        <v>2.284</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0.005303975134295768</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0.006893776250416507</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C101"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>bin_start</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>bin_end</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0.681</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0.77361</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>0.77361</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0.86622</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0.86622</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0.9588300000000001</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>0.9588300000000001</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1.05144</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1.05144</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1.14405</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1.14405</v>
-      </c>
-      <c r="B7" t="n">
-        <v>1.23666</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1.23666</v>
-      </c>
-      <c r="B8" t="n">
-        <v>1.32927</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>1.32927</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1.42188</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>1.42188</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1.51449</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>1.51449</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1.6071</v>
-      </c>
-      <c r="C11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>1.6071</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1.69971</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>1.69971</v>
-      </c>
-      <c r="B13" t="n">
-        <v>1.79232</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>1.79232</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1.88493</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>1.88493</v>
-      </c>
-      <c r="B15" t="n">
-        <v>1.97754</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>1.97754</v>
-      </c>
-      <c r="B16" t="n">
-        <v>2.07015</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>2.07015</v>
-      </c>
-      <c r="B17" t="n">
-        <v>2.16276</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>2.16276</v>
-      </c>
-      <c r="B18" t="n">
-        <v>2.25537</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>2.25537</v>
-      </c>
-      <c r="B19" t="n">
-        <v>2.34798</v>
-      </c>
-      <c r="C19" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>2.34798</v>
-      </c>
-      <c r="B20" t="n">
-        <v>2.44059</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>2.44059</v>
-      </c>
-      <c r="B21" t="n">
-        <v>2.5332</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>2.5332</v>
-      </c>
-      <c r="B22" t="n">
-        <v>2.62581</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>2.62581</v>
-      </c>
-      <c r="B23" t="n">
-        <v>2.71842</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>2.71842</v>
-      </c>
-      <c r="B24" t="n">
-        <v>2.81103</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>2.81103</v>
-      </c>
-      <c r="B25" t="n">
-        <v>2.90364</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>2.90364</v>
-      </c>
-      <c r="B26" t="n">
-        <v>2.99625</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>2.99625</v>
-      </c>
-      <c r="B27" t="n">
-        <v>3.08886</v>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>3.08886</v>
-      </c>
-      <c r="B28" t="n">
-        <v>3.18147</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>3.18147</v>
-      </c>
-      <c r="B29" t="n">
-        <v>3.27408</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>3.27408</v>
-      </c>
-      <c r="B30" t="n">
-        <v>3.36669</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>3.36669</v>
-      </c>
-      <c r="B31" t="n">
-        <v>3.4593</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>3.4593</v>
-      </c>
-      <c r="B32" t="n">
-        <v>3.55191</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>3.55191</v>
-      </c>
-      <c r="B33" t="n">
-        <v>3.64452</v>
-      </c>
-      <c r="C33" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>3.64452</v>
-      </c>
-      <c r="B34" t="n">
-        <v>3.73713</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>3.73713</v>
-      </c>
-      <c r="B35" t="n">
-        <v>3.82974</v>
-      </c>
-      <c r="C35" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>3.82974</v>
-      </c>
-      <c r="B36" t="n">
-        <v>3.92235</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>3.92235</v>
-      </c>
-      <c r="B37" t="n">
-        <v>4.01496</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>4.01496</v>
-      </c>
-      <c r="B38" t="n">
-        <v>4.10757</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>4.10757</v>
-      </c>
-      <c r="B39" t="n">
-        <v>4.20018</v>
-      </c>
-      <c r="C39" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>4.20018</v>
-      </c>
-      <c r="B40" t="n">
-        <v>4.29279</v>
-      </c>
-      <c r="C40" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>4.29279</v>
-      </c>
-      <c r="B41" t="n">
-        <v>4.3854</v>
-      </c>
-      <c r="C41" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>4.3854</v>
-      </c>
-      <c r="B42" t="n">
-        <v>4.478009999999999</v>
-      </c>
-      <c r="C42" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>4.478009999999999</v>
-      </c>
-      <c r="B43" t="n">
-        <v>4.57062</v>
-      </c>
-      <c r="C43" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>4.57062</v>
-      </c>
-      <c r="B44" t="n">
-        <v>4.66323</v>
-      </c>
-      <c r="C44" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>4.66323</v>
-      </c>
-      <c r="B45" t="n">
-        <v>4.75584</v>
-      </c>
-      <c r="C45" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>4.75584</v>
-      </c>
-      <c r="B46" t="n">
-        <v>4.84845</v>
-      </c>
-      <c r="C46" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>4.84845</v>
-      </c>
-      <c r="B47" t="n">
-        <v>4.94106</v>
-      </c>
-      <c r="C47" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>4.94106</v>
-      </c>
-      <c r="B48" t="n">
-        <v>5.03367</v>
-      </c>
-      <c r="C48" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>5.03367</v>
-      </c>
-      <c r="B49" t="n">
-        <v>5.12628</v>
-      </c>
-      <c r="C49" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>5.12628</v>
-      </c>
-      <c r="B50" t="n">
-        <v>5.21889</v>
-      </c>
-      <c r="C50" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>5.21889</v>
-      </c>
-      <c r="B51" t="n">
-        <v>5.3115</v>
-      </c>
-      <c r="C51" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>5.3115</v>
-      </c>
-      <c r="B52" t="n">
-        <v>5.40411</v>
-      </c>
-      <c r="C52" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>5.40411</v>
-      </c>
-      <c r="B53" t="n">
-        <v>5.49672</v>
-      </c>
-      <c r="C53" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>5.49672</v>
-      </c>
-      <c r="B54" t="n">
-        <v>5.58933</v>
-      </c>
-      <c r="C54" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>5.58933</v>
-      </c>
-      <c r="B55" t="n">
-        <v>5.68194</v>
-      </c>
-      <c r="C55" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>5.68194</v>
-      </c>
-      <c r="B56" t="n">
-        <v>5.77455</v>
-      </c>
-      <c r="C56" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>5.77455</v>
-      </c>
-      <c r="B57" t="n">
-        <v>5.86716</v>
-      </c>
-      <c r="C57" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>5.86716</v>
-      </c>
-      <c r="B58" t="n">
-        <v>5.95977</v>
-      </c>
-      <c r="C58" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>5.95977</v>
-      </c>
-      <c r="B59" t="n">
-        <v>6.05238</v>
-      </c>
-      <c r="C59" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>6.05238</v>
-      </c>
-      <c r="B60" t="n">
-        <v>6.14499</v>
-      </c>
-      <c r="C60" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>6.14499</v>
-      </c>
-      <c r="B61" t="n">
-        <v>6.2376</v>
-      </c>
-      <c r="C61" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>6.2376</v>
-      </c>
-      <c r="B62" t="n">
-        <v>6.33021</v>
-      </c>
-      <c r="C62" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>6.33021</v>
-      </c>
-      <c r="B63" t="n">
-        <v>6.42282</v>
-      </c>
-      <c r="C63" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>6.42282</v>
-      </c>
-      <c r="B64" t="n">
-        <v>6.51543</v>
-      </c>
-      <c r="C64" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>6.51543</v>
-      </c>
-      <c r="B65" t="n">
-        <v>6.60804</v>
-      </c>
-      <c r="C65" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>6.60804</v>
-      </c>
-      <c r="B66" t="n">
-        <v>6.70065</v>
-      </c>
-      <c r="C66" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>6.70065</v>
-      </c>
-      <c r="B67" t="n">
-        <v>6.79326</v>
-      </c>
-      <c r="C67" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>6.79326</v>
-      </c>
-      <c r="B68" t="n">
-        <v>6.88587</v>
-      </c>
-      <c r="C68" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>6.88587</v>
-      </c>
-      <c r="B69" t="n">
-        <v>6.97848</v>
-      </c>
-      <c r="C69" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>6.97848</v>
-      </c>
-      <c r="B70" t="n">
-        <v>7.07109</v>
-      </c>
-      <c r="C70" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>7.07109</v>
-      </c>
-      <c r="B71" t="n">
-        <v>7.1637</v>
-      </c>
-      <c r="C71" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>7.1637</v>
-      </c>
-      <c r="B72" t="n">
-        <v>7.25631</v>
-      </c>
-      <c r="C72" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>7.25631</v>
-      </c>
-      <c r="B73" t="n">
-        <v>7.34892</v>
-      </c>
-      <c r="C73" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>7.34892</v>
-      </c>
-      <c r="B74" t="n">
-        <v>7.44153</v>
-      </c>
-      <c r="C74" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>7.44153</v>
-      </c>
-      <c r="B75" t="n">
-        <v>7.53414</v>
-      </c>
-      <c r="C75" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>7.53414</v>
-      </c>
-      <c r="B76" t="n">
-        <v>7.626749999999999</v>
-      </c>
-      <c r="C76" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>7.626749999999999</v>
-      </c>
-      <c r="B77" t="n">
-        <v>7.71936</v>
-      </c>
-      <c r="C77" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>7.71936</v>
-      </c>
-      <c r="B78" t="n">
-        <v>7.81197</v>
-      </c>
-      <c r="C78" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>7.81197</v>
-      </c>
-      <c r="B79" t="n">
-        <v>7.90458</v>
-      </c>
-      <c r="C79" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>7.90458</v>
-      </c>
-      <c r="B80" t="n">
-        <v>7.99719</v>
-      </c>
-      <c r="C80" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>7.99719</v>
-      </c>
-      <c r="B81" t="n">
-        <v>8.0898</v>
-      </c>
-      <c r="C81" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>8.0898</v>
-      </c>
-      <c r="B82" t="n">
-        <v>8.182410000000001</v>
-      </c>
-      <c r="C82" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>8.182410000000001</v>
-      </c>
-      <c r="B83" t="n">
-        <v>8.27502</v>
-      </c>
-      <c r="C83" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>8.27502</v>
-      </c>
-      <c r="B84" t="n">
-        <v>8.36763</v>
-      </c>
-      <c r="C84" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>8.36763</v>
-      </c>
-      <c r="B85" t="n">
-        <v>8.460239999999999</v>
-      </c>
-      <c r="C85" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>8.460239999999999</v>
-      </c>
-      <c r="B86" t="n">
-        <v>8.552849999999999</v>
-      </c>
-      <c r="C86" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>8.552849999999999</v>
-      </c>
-      <c r="B87" t="n">
-        <v>8.64546</v>
-      </c>
-      <c r="C87" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>8.64546</v>
-      </c>
-      <c r="B88" t="n">
-        <v>8.73807</v>
-      </c>
-      <c r="C88" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>8.73807</v>
-      </c>
-      <c r="B89" t="n">
-        <v>8.830680000000001</v>
-      </c>
-      <c r="C89" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>8.830680000000001</v>
-      </c>
-      <c r="B90" t="n">
-        <v>8.923290000000001</v>
-      </c>
-      <c r="C90" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>8.923290000000001</v>
-      </c>
-      <c r="B91" t="n">
-        <v>9.015899999999998</v>
-      </c>
-      <c r="C91" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>9.015899999999998</v>
-      </c>
-      <c r="B92" t="n">
-        <v>9.108509999999999</v>
-      </c>
-      <c r="C92" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>9.108509999999999</v>
-      </c>
-      <c r="B93" t="n">
-        <v>9.20112</v>
-      </c>
-      <c r="C93" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>9.20112</v>
-      </c>
-      <c r="B94" t="n">
-        <v>9.29373</v>
-      </c>
-      <c r="C94" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>9.29373</v>
-      </c>
-      <c r="B95" t="n">
-        <v>9.386340000000001</v>
-      </c>
-      <c r="C95" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>9.386340000000001</v>
-      </c>
-      <c r="B96" t="n">
-        <v>9.478950000000001</v>
-      </c>
-      <c r="C96" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>9.478950000000001</v>
-      </c>
-      <c r="B97" t="n">
-        <v>9.571560000000002</v>
-      </c>
-      <c r="C97" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>9.571560000000002</v>
-      </c>
-      <c r="B98" t="n">
-        <v>9.664169999999999</v>
-      </c>
-      <c r="C98" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>9.664169999999999</v>
-      </c>
-      <c r="B99" t="n">
-        <v>9.756779999999999</v>
-      </c>
-      <c r="C99" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>9.756779999999999</v>
-      </c>
-      <c r="B100" t="n">
-        <v>9.84939</v>
-      </c>
-      <c r="C100" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>9.84939</v>
-      </c>
-      <c r="B101" t="n">
-        <v>9.942</v>
-      </c>
-      <c r="C101" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Parent cpu_op</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Input dims</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Input strides</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Concrete Inputs</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Kernel name</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Short Kernel duration (µs) sum</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Short Kernel count</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Short Kernel duration (µs) mean</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Short Kernel duration (µs) percent of total time</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>aten::add</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>((16, 559, 1), (), ())</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>((559, 1, 1), (), ())</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>('', '', '1')</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;float&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;float&gt;, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>223.305</v>
-      </c>
-      <c r="G2" t="n">
-        <v>49</v>
-      </c>
-      <c r="H2" t="n">
-        <v>4.557244897959184</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.6739994332746314</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>aten::rsqrt</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>((16, 559, 1),)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>((559, 1, 1),)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>('',)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::rsqrt_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::rsqrt_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>215.446</v>
-      </c>
-      <c r="G3" t="n">
-        <v>49</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4.396857142857143</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.6502786856599102</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>aten::fill_</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>((1,), ())</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>((1,), ())</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>('', '0')</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;int&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;int&gt;, std::array&lt;char*, 1ul&gt;)</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>107.545</v>
-      </c>
-      <c r="G4" t="n">
-        <v>24</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.481041666666667</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.3246020870626284</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>aten::neg</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>((16, 16, 559, 32),)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>((572416, 64, 1024, 1),)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>('',)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>55.682</v>
-      </c>
-      <c r="G5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" t="n">
-        <v>9.280333333333333</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.1680644698667653</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>aten::mean</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>((16, 559, 1024), (), (), ())</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>((572416, 1024, 1), (), (), ())</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>('', '[-1]', 'True', '')</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4, 4&gt; &gt;(at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4, 4&gt;)</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>17.758</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" t="n">
-        <v>8.879</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.05359880851790557</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>aten::mul</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>((1, 559, 64), ())</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>((35776, 64, 1), ())</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>('', '')</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>7.415</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3.7075</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.02238062648723222</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>aten::cat</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>(((1, 559, 32), (1, 559, 32)), ())</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>(((17888, 1, 559), (17888, 1, 559)), ())</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>('', '-1')</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>6.333</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>6.333</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.01911483581168465</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>aten::eq</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>((16, 559), ())</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>((559, 1), ())</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>('', '1')</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>5.572</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>5.572</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.01681791649182171</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>aten::cos</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>((1, 559, 64),)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>((35776, 64, 1),)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>('',)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::cos_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::cos_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.01415578398180973</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>aten::sin</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>((1, 559, 64),)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>((35776, 64, 1),)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>('',)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::sin_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sin_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>4.249</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>4.249</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.01282471772680374</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>aten::copy_</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>((1, 1, 559), (1, 1, 559), ())</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>((559, 559, 1), (559, 559, 1), ())</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>('', '', 'False')</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1})</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>3.086</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>3.086</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.009314445494214247</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>aten::copy_</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>((1, 559, 64), (1, 559, 64), ())</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>((35776, 64, 1), (35776, 64, 1), ())</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>('', '', 'False')</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>3.085</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.5425</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.009311427203386569</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>aten::all</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>((16, 559),)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>((559, 1),)</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>('',)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;bool, at::native::func_wrapper_t&lt;bool, at::native::and_kernel_cuda(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, bool)#1}&gt;, unsigned int, bool, 4, 4&gt; &gt;(at::native::ReduceOp&lt;bool, at::native::func_wrapper_t&lt;bool, at::native::and_kernel_cuda(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, bool)#1}&gt;, unsigned int, bool, 4, 4&gt;)</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>2.325</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2.325</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.007017526174351306</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>aten::arange</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>((), (), (), (0,))</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>((), (), (), (1,))</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>('0', '559', '1', '')</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>2.284</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2.284</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.006893776250416507</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -4313,7 +685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4329,25 +701,35 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>total_subtree_kernel_time_sum</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>total_direct_kernel_time_ms</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>total_subtree_kernel_time_ms</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Categories</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>total_direct_kernel_time_ms</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Percentage (%)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Cumulative Percentage (%)</t>
         </is>
@@ -4363,20 +745,26 @@
         <v>8663.615234375</v>
       </c>
       <c r="C2" t="n">
-        <v>96</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>{'GEMM'}</t>
-        </is>
+        <v>8663.615234375</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8.663615234374999</v>
       </c>
       <c r="E2" t="n">
         <v>8.663615234374999</v>
       </c>
       <c r="F2" t="n">
+        <v>96</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>{'GEMM'}</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
         <v>29.12734092062252</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>29.12734092062252</v>
       </c>
     </row>
@@ -4390,20 +778,26 @@
         <v>4541.28857421875</v>
       </c>
       <c r="C3" t="n">
-        <v>220</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>4541.28857421875</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.54128857421875</v>
       </c>
       <c r="E3" t="n">
         <v>4.54128857421875</v>
       </c>
       <c r="F3" t="n">
+        <v>220</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>15.26795188172271</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>44.39529280234522</v>
       </c>
     </row>
@@ -4417,20 +811,26 @@
         <v>3908.79833984375</v>
       </c>
       <c r="C4" t="n">
+        <v>4016.34326171875</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.90879833984375</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.01634326171875</v>
+      </c>
+      <c r="F4" t="n">
         <v>24</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>{'other'}</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>3.90879833984375</v>
-      </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>13.14150025763531</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>57.53679305998053</v>
       </c>
     </row>
@@ -4444,20 +844,26 @@
         <v>3190.6943359375</v>
       </c>
       <c r="C5" t="n">
-        <v>197</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>3190.6943359375</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.1906943359375</v>
       </c>
       <c r="E5" t="n">
         <v>3.1906943359375</v>
       </c>
       <c r="F5" t="n">
+        <v>197</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
         <v>10.72721250680696</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>68.26400556678749</v>
       </c>
     </row>
@@ -4471,20 +877,26 @@
         <v>2954.7626953125</v>
       </c>
       <c r="C6" t="n">
-        <v>72</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>{'GEMM'}</t>
-        </is>
+        <v>2954.7626953125</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.9547626953125</v>
       </c>
       <c r="E6" t="n">
         <v>2.9547626953125</v>
       </c>
       <c r="F6" t="n">
+        <v>72</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>{'GEMM'}</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
         <v>9.934003073500232</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>78.19800864028772</v>
       </c>
     </row>
@@ -4498,20 +910,26 @@
         <v>1895.603515625</v>
       </c>
       <c r="C7" t="n">
-        <v>145</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>1895.603515625</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.895603515625</v>
       </c>
       <c r="E7" t="n">
         <v>1.895603515625</v>
       </c>
       <c r="F7" t="n">
+        <v>145</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
         <v>6.373077330450393</v>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
         <v>84.57108597073812</v>
       </c>
     </row>
@@ -4525,20 +943,26 @@
         <v>1356.06982421875</v>
       </c>
       <c r="C8" t="n">
-        <v>49</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>{'other'}</t>
-        </is>
+        <v>1356.06982421875</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.35606982421875</v>
       </c>
       <c r="E8" t="n">
         <v>1.35606982421875</v>
       </c>
       <c r="F8" t="n">
+        <v>49</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>{'other'}</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
         <v>4.559148463272868</v>
       </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
         <v>89.13023443401099</v>
       </c>
     </row>
@@ -4552,20 +976,26 @@
         <v>928.080078125</v>
       </c>
       <c r="C9" t="n">
-        <v>49</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>928.080078125</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.928080078125</v>
       </c>
       <c r="E9" t="n">
         <v>0.928080078125</v>
       </c>
       <c r="F9" t="n">
+        <v>49</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
         <v>3.120233771454534</v>
       </c>
-      <c r="G9" t="n">
+      <c r="I9" t="n">
         <v>92.25046820546552</v>
       </c>
     </row>
@@ -4579,20 +1009,26 @@
         <v>777.642578125</v>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>777.642578125</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.777642578125</v>
       </c>
       <c r="E10" t="n">
         <v>0.777642578125</v>
       </c>
       <c r="F10" t="n">
+        <v>24</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
         <v>2.61445826882601</v>
       </c>
-      <c r="G10" t="n">
+      <c r="I10" t="n">
         <v>94.86492647429154</v>
       </c>
     </row>
@@ -4606,20 +1042,26 @@
         <v>619.05224609375</v>
       </c>
       <c r="C11" t="n">
-        <v>49</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>{'reduce'}</t>
-        </is>
+        <v>619.05224609375</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.61905224609375</v>
       </c>
       <c r="E11" t="n">
         <v>0.61905224609375</v>
       </c>
       <c r="F11" t="n">
+        <v>49</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>{'reduce'}</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
         <v>2.081272694118042</v>
       </c>
-      <c r="G11" t="n">
+      <c r="I11" t="n">
         <v>96.94619916840958</v>
       </c>
     </row>
@@ -4633,20 +1075,26 @@
         <v>517.09814453125</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>517.09814453125</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.51709814453125</v>
       </c>
       <c r="E12" t="n">
         <v>0.51709814453125</v>
       </c>
       <c r="F12" t="n">
+        <v>48</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
         <v>1.738499868440847</v>
       </c>
-      <c r="G12" t="n">
+      <c r="I12" t="n">
         <v>98.68469903685042</v>
       </c>
     </row>
@@ -4660,20 +1108,26 @@
         <v>215.44775390625</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>215.44775390625</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.21544775390625</v>
       </c>
       <c r="E13" t="n">
         <v>0.21544775390625</v>
       </c>
       <c r="F13" t="n">
+        <v>49</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
         <v>0.7243419760506528</v>
       </c>
-      <c r="G13" t="n">
+      <c r="I13" t="n">
         <v>99.40904101290107</v>
       </c>
     </row>
@@ -4687,20 +1141,26 @@
         <v>107.544921875</v>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>107.544921875</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.107544921875</v>
       </c>
       <c r="E14" t="n">
         <v>0.107544921875</v>
       </c>
       <c r="F14" t="n">
+        <v>24</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
         <v>0.3615693355478085</v>
       </c>
-      <c r="G14" t="n">
+      <c r="I14" t="n">
         <v>99.77061034844888</v>
       </c>
     </row>
@@ -4714,20 +1174,26 @@
         <v>27.341796875</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>{'GEMM'}</t>
-        </is>
+        <v>27.341796875</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.027341796875</v>
       </c>
       <c r="E15" t="n">
         <v>0.027341796875</v>
       </c>
       <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>{'GEMM'}</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
         <v>0.09192396215850518</v>
       </c>
-      <c r="G15" t="n">
+      <c r="I15" t="n">
         <v>99.86253431060739</v>
       </c>
     </row>
@@ -4741,20 +1207,26 @@
         <v>21.0078125</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>{'other'}</t>
-        </is>
+        <v>21.0078125</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.0210078125</v>
       </c>
       <c r="E16" t="n">
         <v>0.0210078125</v>
       </c>
       <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>{'other'}</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
         <v>0.07062891184919506</v>
       </c>
-      <c r="G16" t="n">
+      <c r="I16" t="n">
         <v>99.93316322245659</v>
       </c>
     </row>
@@ -4768,20 +1240,26 @@
         <v>5.57177734375</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>5.57177734375</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.00557177734375</v>
       </c>
       <c r="E17" t="n">
         <v>0.00557177734375</v>
       </c>
       <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
         <v>0.01873248682389282</v>
       </c>
-      <c r="G17" t="n">
+      <c r="I17" t="n">
         <v>99.95189570928048</v>
       </c>
     </row>
@@ -4795,20 +1273,26 @@
         <v>4.68994140625</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>4.68994140625</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.00468994140625</v>
       </c>
       <c r="E18" t="n">
         <v>0.00468994140625</v>
       </c>
       <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
         <v>0.01576772727574188</v>
       </c>
-      <c r="G18" t="n">
+      <c r="I18" t="n">
         <v>99.96766343655622</v>
       </c>
     </row>
@@ -4822,20 +1306,26 @@
         <v>4.2490234375</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>{'elementwise'}</t>
-        </is>
+        <v>4.2490234375</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.0042490234375</v>
       </c>
       <c r="E19" t="n">
         <v>0.0042490234375</v>
       </c>
       <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>{'elementwise'}</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
         <v>0.0142853475016664</v>
       </c>
-      <c r="G19" t="n">
+      <c r="I19" t="n">
         <v>99.98194878405789</v>
       </c>
     </row>
@@ -4849,20 +1339,26 @@
         <v>2.3251953125</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>{'reduce'}</t>
-        </is>
+        <v>2.3251953125</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.0023251953125</v>
       </c>
       <c r="E20" t="n">
         <v>0.0023251953125</v>
       </c>
       <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>{'reduce'}</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
         <v>0.007817378166276191</v>
       </c>
-      <c r="G20" t="n">
+      <c r="I20" t="n">
         <v>99.98976616222417</v>
       </c>
     </row>
@@ -4876,20 +1372,26 @@
         <v>2.2841796875</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>{'other'}</t>
-        </is>
+        <v>2.2841796875</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.0022841796875</v>
       </c>
       <c r="E21" t="n">
         <v>0.0022841796875</v>
       </c>
       <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>{'other'}</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
         <v>0.007679482373338938</v>
       </c>
-      <c r="G21" t="n">
+      <c r="I21" t="n">
         <v>99.99744564459751</v>
       </c>
     </row>
@@ -4903,20 +1405,26 @@
         <v>0.759765625</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>{'other'}</t>
-        </is>
+        <v>0.759765625</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.000759765625</v>
       </c>
       <c r="E22" t="n">
         <v>0.000759765625</v>
       </c>
       <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>{'other'}</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
         <v>0.002554355402504358</v>
       </c>
-      <c r="G22" t="n">
+      <c r="I22" t="n">
         <v>100</v>
       </c>
     </row>
@@ -4931,7 +1439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U37"/>
+  <dimension ref="A1:AA37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4992,50 +1500,80 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>total_subtree_kernel_time_mean</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>total_direct_kernel_time_median</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>total_subtree_kernel_time_median</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_std</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>total_subtree_kernel_time_std</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_min</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>total_subtree_kernel_time_min</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_max</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>total_subtree_kernel_time_max</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>total_direct_kernel_time_sum</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>total_subtree_kernel_time_sum</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>ex_UID</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>kernel_details_summary</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Percentage (%)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Cumulative Percentage (%)</t>
         </is>
@@ -5094,37 +1632,55 @@
         <v>110.5890299479167</v>
       </c>
       <c r="L2" t="n">
+        <v>110.5890299479167</v>
+      </c>
+      <c r="M2" t="n">
         <v>110.452880859375</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
+        <v>110.452880859375</v>
+      </c>
+      <c r="O2" t="n">
         <v>3.280588398059727</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
+        <v>3.280588398059727</v>
+      </c>
+      <c r="Q2" t="n">
         <v>105</v>
       </c>
-      <c r="O2" t="n">
+      <c r="R2" t="n">
+        <v>105</v>
+      </c>
+      <c r="S2" t="n">
         <v>118.55078125</v>
       </c>
-      <c r="P2" t="n">
+      <c r="T2" t="n">
+        <v>118.55078125</v>
+      </c>
+      <c r="U2" t="n">
         <v>5308.2734375</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="V2" t="n">
+        <v>5308.2734375</v>
+      </c>
+      <c r="W2" t="n">
         <v>231</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x224x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA512_LBSPPB128_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT4_7_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW4_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA4_VWB1_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 48, 'total_duration_us': np.float64(5308.273), 'mean_duration_us': np.float64(110.58902083333334), 'median_duration_us': np.float64(110.453), 'std_dev_duration_us': np.float64(3.2462516941953186), 'min_duration_us': np.float64(105.0), 'max_duration_us': np.float64(118.551)}]</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT128x224x64_MI16x...', 'stream': 0, 'mean_duration_us': np.float64(110.59)}]</t>
         </is>
       </c>
-      <c r="T2" t="n">
+      <c r="Z2" t="n">
         <v>17.8465785854006</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AA2" t="n">
         <v>17.8465785854006</v>
       </c>
     </row>
@@ -5181,37 +1737,55 @@
         <v>162.8665974934896</v>
       </c>
       <c r="L3" t="n">
+        <v>167.3476359049479</v>
+      </c>
+      <c r="M3" t="n">
         <v>164.237060546875</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
+        <v>168.906494140625</v>
+      </c>
+      <c r="O3" t="n">
         <v>9.452351716739908</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
+        <v>10.23520398355555</v>
+      </c>
+      <c r="Q3" t="n">
         <v>138.55712890625</v>
       </c>
-      <c r="O3" t="n">
+      <c r="R3" t="n">
+        <v>139.55908203125</v>
+      </c>
+      <c r="S3" t="n">
         <v>173.0771484375</v>
       </c>
-      <c r="P3" t="n">
+      <c r="T3" t="n">
+        <v>177.92724609375</v>
+      </c>
+      <c r="U3" t="n">
         <v>3908.79833984375</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="V3" t="n">
+        <v>4016.34326171875</v>
+      </c>
+      <c r="W3" t="n">
         <v>165</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>[{'name': 'attn_fwd', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(3908.798), 'mean_duration_us': np.float64(162.86658333333332), 'median_duration_us': np.float64(164.23700000000002), 'std_dev_duration_us': np.float64(9.253315184825505), 'min_duration_us': np.float64(138.557), 'max_duration_us': np.float64(173.077)}]</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>[{'name': 'attn_fwd', 'stream': 0, 'mean_duration_us': np.float64(162.87)}]</t>
         </is>
       </c>
-      <c r="T3" t="n">
+      <c r="Z3" t="n">
         <v>13.14150025763531</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AA3" t="n">
         <v>30.98807884303591</v>
       </c>
     </row>
@@ -5268,37 +1842,55 @@
         <v>41.03837076822916</v>
       </c>
       <c r="L4" t="n">
+        <v>41.03837076822916</v>
+      </c>
+      <c r="M4" t="n">
         <v>40.71240234375</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
+        <v>40.71240234375</v>
+      </c>
+      <c r="O4" t="n">
         <v>1.121361742339089</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
+        <v>1.121361742339089</v>
+      </c>
+      <c r="Q4" t="n">
         <v>39.56982421875</v>
       </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
+        <v>39.56982421875</v>
+      </c>
+      <c r="S4" t="n">
         <v>45.02294921875</v>
       </c>
-      <c r="P4" t="n">
+      <c r="T4" t="n">
+        <v>45.02294921875</v>
+      </c>
+      <c r="U4" t="n">
         <v>2954.7626953125</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="V4" t="n">
+        <v>2954.7626953125</v>
+      </c>
+      <c r="W4" t="n">
         <v>90</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 72, 'total_duration_us': np.float64(2954.763), 'mean_duration_us': np.float64(41.038375), 'median_duration_us': np.float64(40.7125), 'std_dev_duration_us': np.float64(1.1135532272552386), 'min_duration_us': np.float64(39.57), 'max_duration_us': np.float64(45.023)}]</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x...', 'stream': 0, 'mean_duration_us': np.float64(41.04)}]</t>
         </is>
       </c>
-      <c r="T4" t="n">
+      <c r="Z4" t="n">
         <v>9.93400307350023</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AA4" t="n">
         <v>40.92208191653614</v>
       </c>
     </row>
@@ -5355,37 +1947,55 @@
         <v>98.94974772135417</v>
       </c>
       <c r="L5" t="n">
+        <v>98.94974772135417</v>
+      </c>
+      <c r="M5" t="n">
         <v>98.324951171875</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
+        <v>98.324951171875</v>
+      </c>
+      <c r="O5" t="n">
         <v>3.384941704730123</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
+        <v>3.384941704730123</v>
+      </c>
+      <c r="Q5" t="n">
         <v>93.65380859375</v>
       </c>
-      <c r="O5" t="n">
+      <c r="R5" t="n">
+        <v>93.65380859375</v>
+      </c>
+      <c r="S5" t="n">
         <v>105.8828125</v>
       </c>
-      <c r="P5" t="n">
+      <c r="T5" t="n">
+        <v>105.8828125</v>
+      </c>
+      <c r="U5" t="n">
         <v>2374.7939453125</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="V5" t="n">
+        <v>2374.7939453125</v>
+      </c>
+      <c r="W5" t="n">
         <v>253</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(2374.795), 'mean_duration_us': np.float64(98.94979166666667), 'median_duration_us': np.float64(98.32499999999999), 'std_dev_duration_us': np.float64(3.3136632546066833), 'min_duration_us': np.float64(93.654), 'max_duration_us': np.float64(105.883)}]</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x...', 'stream': 0, 'mean_duration_us': np.float64(98.95)}]</t>
         </is>
       </c>
-      <c r="T5" t="n">
+      <c r="Z5" t="n">
         <v>7.984130295502148</v>
       </c>
-      <c r="U5" t="n">
+      <c r="AA5" t="n">
         <v>48.90621221203828</v>
       </c>
     </row>
@@ -5442,37 +2052,55 @@
         <v>28.11951700846354</v>
       </c>
       <c r="L6" t="n">
+        <v>28.11951700846354</v>
+      </c>
+      <c r="M6" t="n">
         <v>27.90283203125</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
+        <v>27.90283203125</v>
+      </c>
+      <c r="O6" t="n">
         <v>0.8371311008823814</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
+        <v>0.8371311008823814</v>
+      </c>
+      <c r="Q6" t="n">
         <v>26.81982421875</v>
       </c>
-      <c r="O6" t="n">
+      <c r="R6" t="n">
+        <v>26.81982421875</v>
+      </c>
+      <c r="S6" t="n">
         <v>30.34814453125</v>
       </c>
-      <c r="P6" t="n">
+      <c r="T6" t="n">
+        <v>30.34814453125</v>
+      </c>
+      <c r="U6" t="n">
         <v>1349.73681640625</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="V6" t="n">
+        <v>1349.73681640625</v>
+      </c>
+      <c r="W6" t="n">
         <v>130</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 4, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 0, 'count': 48, 'total_duration_us': np.float64(1349.738), 'mean_duration_us': np.float64(28.119541666666667), 'median_duration_us': np.float64(27.903), 'std_dev_duration_us': np.float64(0.8283528575415325), 'min_duration_us': np.float64(26.82), 'max_duration_us': np.float64(30.348)}]</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::...', 'stream': 0, 'mean_duration_us': np.float64(28.12)}]</t>
         </is>
       </c>
-      <c r="T6" t="n">
+      <c r="Z6" t="n">
         <v>4.537856696196722</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AA6" t="n">
         <v>53.444068908235</v>
       </c>
     </row>
@@ -5529,37 +2157,55 @@
         <v>23.55439851721939</v>
       </c>
       <c r="L7" t="n">
+        <v>23.55439851721939</v>
+      </c>
+      <c r="M7" t="n">
         <v>23.453125</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
+        <v>23.453125</v>
+      </c>
+      <c r="O7" t="n">
         <v>1.710600521974922</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
+        <v>1.710600521974922</v>
+      </c>
+      <c r="Q7" t="n">
         <v>18.44091796875</v>
       </c>
-      <c r="O7" t="n">
+      <c r="R7" t="n">
+        <v>18.44091796875</v>
+      </c>
+      <c r="S7" t="n">
         <v>27.22119140625</v>
       </c>
-      <c r="P7" t="n">
+      <c r="T7" t="n">
+        <v>27.22119140625</v>
+      </c>
+      <c r="U7" t="n">
         <v>1154.16552734375</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="V7" t="n">
+        <v>1154.16552734375</v>
+      </c>
+      <c r="W7" t="n">
         <v>78</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 49, 'total_duration_us': np.float64(1154.1640000000002), 'mean_duration_us': np.float64(23.55436734693878), 'median_duration_us': np.float64(23.453), 'std_dev_duration_us': np.float64(1.6930433736488344), 'min_duration_us': np.float64(18.441), 'max_duration_us': np.float64(27.221)}]</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 4, at::na...', 'stream': 0, 'mean_duration_us': np.float64(23.55)}]</t>
         </is>
       </c>
-      <c r="T7" t="n">
+      <c r="Z7" t="n">
         <v>3.880340006373412</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AA7" t="n">
         <v>57.32440891460841</v>
       </c>
     </row>
@@ -5616,37 +2262,55 @@
         <v>15.11367458767361</v>
       </c>
       <c r="L8" t="n">
+        <v>15.11367458767361</v>
+      </c>
+      <c r="M8" t="n">
         <v>15.19287109375</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
+        <v>15.19287109375</v>
+      </c>
+      <c r="O8" t="n">
         <v>0.5665176534834554</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
+        <v>0.5665176534834554</v>
+      </c>
+      <c r="Q8" t="n">
         <v>12.98779296875</v>
       </c>
-      <c r="O8" t="n">
+      <c r="R8" t="n">
+        <v>12.98779296875</v>
+      </c>
+      <c r="S8" t="n">
         <v>16.27587890625</v>
       </c>
-      <c r="P8" t="n">
+      <c r="T8" t="n">
+        <v>16.27587890625</v>
+      </c>
+      <c r="U8" t="n">
         <v>1088.1845703125</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="V8" t="n">
+        <v>1088.1845703125</v>
+      </c>
+      <c r="W8" t="n">
         <v>146</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 72, 'total_duration_us': np.float64(1088.184), 'mean_duration_us': np.float64(15.113666666666667), 'median_duration_us': np.float64(15.193), 'std_dev_duration_us': np.float64(0.5625623422242988), 'min_duration_us': np.float64(12.988), 'max_duration_us': np.float64(16.276)}]</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(15.11)}]</t>
         </is>
       </c>
-      <c r="T8" t="n">
+      <c r="Z8" t="n">
         <v>3.658509999185101</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AA8" t="n">
         <v>60.98291891379351</v>
       </c>
     </row>
@@ -5703,37 +2367,55 @@
         <v>21.53999920280612</v>
       </c>
       <c r="L9" t="n">
+        <v>21.53999920280612</v>
+      </c>
+      <c r="M9" t="n">
         <v>21.68896484375</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
+        <v>21.68896484375</v>
+      </c>
+      <c r="O9" t="n">
         <v>0.9070504525026997</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
+        <v>0.9070504525026997</v>
+      </c>
+      <c r="Q9" t="n">
         <v>17.72021484375</v>
       </c>
-      <c r="O9" t="n">
+      <c r="R9" t="n">
+        <v>17.72021484375</v>
+      </c>
+      <c r="S9" t="n">
         <v>23.01220703125</v>
       </c>
-      <c r="P9" t="n">
+      <c r="T9" t="n">
+        <v>23.01220703125</v>
+      </c>
+      <c r="U9" t="n">
         <v>1055.4599609375</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="V9" t="n">
+        <v>1055.4599609375</v>
+      </c>
+      <c r="W9" t="n">
         <v>71</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 49, 'total_duration_us': np.float64(1055.46), 'mean_duration_us': np.float64(21.54), 'median_duration_us': np.float64(21.689), 'std_dev_duration_us': np.float64(0.8977721405381941), 'min_duration_us': np.float64(17.72), 'max_duration_us': np.float64(23.012)}]</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': np.float64(21.54)}]</t>
         </is>
       </c>
-      <c r="T9" t="n">
+      <c r="Z9" t="n">
         <v>3.548488855820164</v>
       </c>
-      <c r="U9" t="n">
+      <c r="AA9" t="n">
         <v>64.53140776961368</v>
       </c>
     </row>
@@ -5790,37 +2472,55 @@
         <v>20.47682698567708</v>
       </c>
       <c r="L10" t="n">
+        <v>20.47682698567708</v>
+      </c>
+      <c r="M10" t="n">
         <v>20.406005859375</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
+        <v>20.406005859375</v>
+      </c>
+      <c r="O10" t="n">
         <v>0.9517316900632534</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
+        <v>0.9517316900632534</v>
+      </c>
+      <c r="Q10" t="n">
         <v>18.8017578125</v>
       </c>
-      <c r="O10" t="n">
+      <c r="R10" t="n">
+        <v>18.8017578125</v>
+      </c>
+      <c r="S10" t="n">
         <v>23.1318359375</v>
       </c>
-      <c r="P10" t="n">
+      <c r="T10" t="n">
+        <v>23.1318359375</v>
+      </c>
+      <c r="U10" t="n">
         <v>982.8876953125</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="V10" t="n">
+        <v>982.8876953125</v>
+      </c>
+      <c r="W10" t="n">
         <v>132</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 48, 'total_duration_us': np.float64(982.889), 'mean_duration_us': np.float64(20.476854166666666), 'median_duration_us': np.float64(20.406), 'std_dev_duration_us': np.float64(0.94175673587502), 'min_duration_us': np.float64(18.802), 'max_duration_us': np.float64(23.132)}]</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(20.48)}]</t>
         </is>
       </c>
-      <c r="T10" t="n">
+      <c r="Z10" t="n">
         <v>3.304498666383521</v>
       </c>
-      <c r="U10" t="n">
+      <c r="AA10" t="n">
         <v>67.8359064359972</v>
       </c>
     </row>
@@ -5877,37 +2577,55 @@
         <v>40.85616048177084</v>
       </c>
       <c r="L11" t="n">
+        <v>40.85616048177084</v>
+      </c>
+      <c r="M11" t="n">
         <v>40.532470703125</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
+        <v>40.532470703125</v>
+      </c>
+      <c r="O11" t="n">
         <v>1.381501226013306</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
+        <v>1.381501226013306</v>
+      </c>
+      <c r="Q11" t="n">
         <v>39.208984375</v>
       </c>
-      <c r="O11" t="n">
+      <c r="R11" t="n">
+        <v>39.208984375</v>
+      </c>
+      <c r="S11" t="n">
         <v>44.94287109375</v>
       </c>
-      <c r="P11" t="n">
+      <c r="T11" t="n">
+        <v>44.94287109375</v>
+      </c>
+      <c r="U11" t="n">
         <v>980.5478515625</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="V11" t="n">
+        <v>980.5478515625</v>
+      </c>
+      <c r="W11" t="n">
         <v>204</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA8_GRVWB8_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA1024_LBSPPB512_LBSPPM0_LPA16_LPB16_LPM0_LRVW8_LWPMn1_MIAV0_MIWT8_4_MO40_NTn1_NTA0_NTB0_NTC0_NTD0_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW8_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA8_VWB4_WSGRA0_WSGRB0_WS64_WG32_8_1', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(980.549), 'mean_duration_us': np.float64(40.856208333333335), 'median_duration_us': np.float64(40.5325), 'std_dev_duration_us': np.float64(1.3524004269928913), 'min_duration_us': np.float64(39.209), 'max_duration_us': np.float64(44.943)}]</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>[{'name': 'Cijk_Alik_Bljk_B_BS_BH_Bias_HA_S_SAV_UserArgs_MT256x128x64_MI16x...', 'stream': 0, 'mean_duration_us': np.float64(40.86)}]</t>
         </is>
       </c>
-      <c r="T11" t="n">
+      <c r="Z11" t="n">
         <v>3.296632039719767</v>
       </c>
-      <c r="U11" t="n">
+      <c r="AA11" t="n">
         <v>71.13253847571697</v>
       </c>
     </row>
@@ -5964,37 +2682,55 @@
         <v>19.89802042643229</v>
       </c>
       <c r="L12" t="n">
+        <v>19.89802042643229</v>
+      </c>
+      <c r="M12" t="n">
         <v>20.044921875</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
+        <v>20.044921875</v>
+      </c>
+      <c r="O12" t="n">
         <v>1.092918112053265</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
+        <v>1.092918112053265</v>
+      </c>
+      <c r="Q12" t="n">
         <v>18.12109375</v>
       </c>
-      <c r="O12" t="n">
+      <c r="R12" t="n">
+        <v>18.12109375</v>
+      </c>
+      <c r="S12" t="n">
         <v>22.73095703125</v>
       </c>
-      <c r="P12" t="n">
+      <c r="T12" t="n">
+        <v>22.73095703125</v>
+      </c>
+      <c r="U12" t="n">
         <v>955.10498046875</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="V12" t="n">
+        <v>955.10498046875</v>
+      </c>
+      <c r="W12" t="n">
         <v>124</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 48, 'total_duration_us': np.float64(955.105), 'mean_duration_us': np.float64(19.898020833333334), 'median_duration_us': np.float64(20.045), 'std_dev_duration_us': np.float64(1.0814598060334801), 'min_duration_us': np.float64(18.121), 'max_duration_us': np.float64(22.731)}]</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(19.9)}]</t>
         </is>
       </c>
-      <c r="T12" t="n">
+      <c r="Z12" t="n">
         <v>3.21109232445094</v>
       </c>
-      <c r="U12" t="n">
+      <c r="AA12" t="n">
         <v>74.34363080016792</v>
       </c>
     </row>
@@ -6051,37 +2787,55 @@
         <v>18.94040975765306</v>
       </c>
       <c r="L13" t="n">
+        <v>18.94040975765306</v>
+      </c>
+      <c r="M13" t="n">
         <v>19.001953125</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
+        <v>19.001953125</v>
+      </c>
+      <c r="O13" t="n">
         <v>1.348781311268545</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
+        <v>1.348781311268545</v>
+      </c>
+      <c r="Q13" t="n">
         <v>14.03076171875</v>
       </c>
-      <c r="O13" t="n">
+      <c r="R13" t="n">
+        <v>14.03076171875</v>
+      </c>
+      <c r="S13" t="n">
         <v>21.93017578125</v>
       </c>
-      <c r="P13" t="n">
+      <c r="T13" t="n">
+        <v>21.93017578125</v>
+      </c>
+      <c r="U13" t="n">
         <v>928.080078125</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="V13" t="n">
+        <v>928.080078125</v>
+      </c>
+      <c r="W13" t="n">
         <v>72</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(anonymous namespace)::pow_tensor_scalar_kernel_impl&lt;float, float&gt;(at::TensorIteratorBase&amp;, float)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::pow_tensor_scalar_kernel_impl&lt;float, float&gt;(at::TensorIteratorBase&amp;, float)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 49, 'total_duration_us': np.float64(928.082), 'mean_duration_us': np.float64(18.940448979591835), 'median_duration_us': np.float64(19.002), 'std_dev_duration_us': np.float64(1.334943231403638), 'min_duration_us': np.float64(14.031), 'max_duration_us': np.float64(21.93)}]</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::(a...', 'stream': 0, 'mean_duration_us': np.float64(18.94)}]</t>
         </is>
       </c>
-      <c r="T13" t="n">
+      <c r="Z13" t="n">
         <v>3.120233771454533</v>
       </c>
-      <c r="U13" t="n">
+      <c r="AA13" t="n">
         <v>77.46386457162245</v>
       </c>
     </row>
@@ -6138,37 +2892,55 @@
         <v>37.87921142578125</v>
       </c>
       <c r="L14" t="n">
+        <v>37.87921142578125</v>
+      </c>
+      <c r="M14" t="n">
         <v>37.464599609375</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
+        <v>37.464599609375</v>
+      </c>
+      <c r="O14" t="n">
         <v>1.628049214737037</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
+        <v>1.628049214737037</v>
+      </c>
+      <c r="Q14" t="n">
         <v>35.39990234375</v>
       </c>
-      <c r="O14" t="n">
+      <c r="R14" t="n">
+        <v>35.39990234375</v>
+      </c>
+      <c r="S14" t="n">
         <v>42.4970703125</v>
       </c>
-      <c r="P14" t="n">
+      <c r="T14" t="n">
+        <v>42.4970703125</v>
+      </c>
+      <c r="U14" t="n">
         <v>909.10107421875</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="V14" t="n">
+        <v>909.10107421875</v>
+      </c>
+      <c r="W14" t="n">
         <v>245</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(909.1), 'mean_duration_us': np.float64(37.87916666666667), 'median_duration_us': np.float64(37.4645), 'std_dev_duration_us': np.float64(1.5937641154059015), 'min_duration_us': np.float64(35.4), 'max_duration_us': np.float64(42.497)}]</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::Bi...', 'stream': 0, 'mean_duration_us': np.float64(37.88)}]</t>
         </is>
       </c>
-      <c r="T14" t="n">
+      <c r="Z14" t="n">
         <v>3.056425776505985</v>
       </c>
-      <c r="U14" t="n">
+      <c r="AA14" t="n">
         <v>80.52029034812844</v>
       </c>
     </row>
@@ -6225,37 +2997,55 @@
         <v>16.26974051339286</v>
       </c>
       <c r="L15" t="n">
+        <v>16.26974051339286</v>
+      </c>
+      <c r="M15" t="n">
         <v>16.0361328125</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
+        <v>16.0361328125</v>
+      </c>
+      <c r="O15" t="n">
         <v>1.155779257306736</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
+        <v>1.155779257306736</v>
+      </c>
+      <c r="Q15" t="n">
         <v>13.02880859375</v>
       </c>
-      <c r="O15" t="n">
+      <c r="R15" t="n">
+        <v>13.02880859375</v>
+      </c>
+      <c r="S15" t="n">
         <v>18.52197265625</v>
       </c>
-      <c r="P15" t="n">
+      <c r="T15" t="n">
+        <v>18.52197265625</v>
+      </c>
+      <c r="U15" t="n">
         <v>797.21728515625</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="V15" t="n">
+        <v>797.21728515625</v>
+      </c>
+      <c r="W15" t="n">
         <v>83</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 49, 'total_duration_us': np.float64(797.2189999999999), 'mean_duration_us': np.float64(16.26977551020408), 'median_duration_us': np.float64(16.036), 'std_dev_duration_us': np.float64(1.143927913836056), 'min_duration_us': np.float64(13.029), 'max_duration_us': np.float64(18.522)}]</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(16.27)}]</t>
         </is>
       </c>
-      <c r="T15" t="n">
+      <c r="Z15" t="n">
         <v>2.680269036005314</v>
       </c>
-      <c r="U15" t="n">
+      <c r="AA15" t="n">
         <v>83.20055938413375</v>
       </c>
     </row>
@@ -6312,37 +3102,55 @@
         <v>32.40177408854166</v>
       </c>
       <c r="L16" t="n">
+        <v>32.40177408854166</v>
+      </c>
+      <c r="M16" t="n">
         <v>32.27294921875</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
+        <v>32.27294921875</v>
+      </c>
+      <c r="O16" t="n">
         <v>0.8776191306910622</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
+        <v>0.8776191306910622</v>
+      </c>
+      <c r="Q16" t="n">
         <v>31.47119140625</v>
       </c>
-      <c r="O16" t="n">
+      <c r="R16" t="n">
+        <v>31.47119140625</v>
+      </c>
+      <c r="S16" t="n">
         <v>35.080078125</v>
       </c>
-      <c r="P16" t="n">
+      <c r="T16" t="n">
+        <v>35.080078125</v>
+      </c>
+      <c r="U16" t="n">
         <v>777.642578125</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="V16" t="n">
+        <v>777.642578125</v>
+      </c>
+      <c r="W16" t="n">
         <v>234</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::(anonymous namespace)::silu_kernel(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#6}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::(anonymous namespace)::silu_kernel(at::TensorIteratorBase&amp;)::{lambda()#1}::operator()() const::{lambda()#6}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(777.643), 'mean_duration_us': np.float64(32.40179166666667), 'median_duration_us': np.float64(32.272999999999996), 'std_dev_duration_us': np.float64(0.8591138835629157), 'min_duration_us': np.float64(31.471), 'max_duration_us': np.float64(35.08)}]</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::(a...', 'stream': 0, 'mean_duration_us': np.float64(32.4)}]</t>
         </is>
       </c>
-      <c r="T16" t="n">
+      <c r="Z16" t="n">
         <v>2.61445826882601</v>
       </c>
-      <c r="U16" t="n">
+      <c r="AA16" t="n">
         <v>85.81501765295977</v>
       </c>
     </row>
@@ -6399,37 +3207,55 @@
         <v>14.96426391601562</v>
       </c>
       <c r="L17" t="n">
+        <v>14.96426391601562</v>
+      </c>
+      <c r="M17" t="n">
         <v>14.873046875</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
+        <v>14.873046875</v>
+      </c>
+      <c r="O17" t="n">
         <v>0.5173983809662352</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
+        <v>0.5173983809662352</v>
+      </c>
+      <c r="Q17" t="n">
         <v>13.14892578125</v>
       </c>
-      <c r="O17" t="n">
+      <c r="R17" t="n">
+        <v>13.14892578125</v>
+      </c>
+      <c r="S17" t="n">
         <v>16.55712890625</v>
       </c>
-      <c r="P17" t="n">
+      <c r="T17" t="n">
+        <v>16.55712890625</v>
+      </c>
+      <c r="U17" t="n">
         <v>718.28466796875</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="V17" t="n">
+        <v>718.28466796875</v>
+      </c>
+      <c r="W17" t="n">
         <v>131</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; &gt;(at::TensorIteratorBase&amp;, at::native::BinaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt; const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 48, 'total_duration_us': np.float64(718.2850000000001), 'mean_duration_us': np.float64(14.964270833333336), 'median_duration_us': np.float64(14.873), 'std_dev_duration_us': np.float64(0.511951932134231), 'min_duration_us': np.float64(13.149), 'max_duration_us': np.float64(16.557)}]</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(14.96)}]</t>
         </is>
       </c>
-      <c r="T17" t="n">
+      <c r="Z17" t="n">
         <v>2.4148951489639</v>
       </c>
-      <c r="U17" t="n">
+      <c r="AA17" t="n">
         <v>88.22991280192366</v>
       </c>
     </row>
@@ -6486,37 +3312,55 @@
         <v>14.36275227864583</v>
       </c>
       <c r="L18" t="n">
+        <v>14.36275227864583</v>
+      </c>
+      <c r="M18" t="n">
         <v>14.35205078125</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
+        <v>14.35205078125</v>
+      </c>
+      <c r="O18" t="n">
         <v>0.5517010273075365</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
+        <v>0.5517010273075365</v>
+      </c>
+      <c r="Q18" t="n">
         <v>13.6298828125</v>
       </c>
-      <c r="O18" t="n">
+      <c r="R18" t="n">
+        <v>13.6298828125</v>
+      </c>
+      <c r="S18" t="n">
         <v>16.7177734375</v>
       </c>
-      <c r="P18" t="n">
+      <c r="T18" t="n">
+        <v>16.7177734375</v>
+      </c>
+      <c r="U18" t="n">
         <v>689.412109375</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="V18" t="n">
+        <v>689.412109375</v>
+      </c>
+      <c r="W18" t="n">
         <v>207</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 0, 'count': 48, 'total_duration_us': np.float64(689.413), 'mean_duration_us': np.float64(14.362770833333334), 'median_duration_us': np.float64(14.352), 'std_dev_duration_us': np.float64(0.5459252558570988), 'min_duration_us': np.float64(13.63), 'max_duration_us': np.float64(16.718)}]</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;8, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(14.36)}]</t>
         </is>
       </c>
-      <c r="T18" t="n">
+      <c r="Z18" t="n">
         <v>2.317824718818987</v>
       </c>
-      <c r="U18" t="n">
+      <c r="AA18" t="n">
         <v>90.54773752074264</v>
       </c>
     </row>
@@ -6573,37 +3417,55 @@
         <v>13.90765505420918</v>
       </c>
       <c r="L19" t="n">
+        <v>13.90765505420918</v>
+      </c>
+      <c r="M19" t="n">
         <v>13.7900390625</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
+        <v>13.7900390625</v>
+      </c>
+      <c r="O19" t="n">
         <v>0.8931457341508564</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
+        <v>0.8931457341508564</v>
+      </c>
+      <c r="Q19" t="n">
         <v>10.14208984375</v>
       </c>
-      <c r="O19" t="n">
+      <c r="R19" t="n">
+        <v>10.14208984375</v>
+      </c>
+      <c r="S19" t="n">
         <v>15.71484375</v>
       </c>
-      <c r="P19" t="n">
+      <c r="T19" t="n">
+        <v>15.71484375</v>
+      </c>
+      <c r="U19" t="n">
         <v>681.47509765625</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="V19" t="n">
+        <v>681.47509765625</v>
+      </c>
+      <c r="W19" t="n">
         <v>82</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 49, 'total_duration_us': np.float64(681.476), 'mean_duration_us': np.float64(13.907673469387754), 'median_duration_us': np.float64(13.79), 'std_dev_duration_us': np.float64(0.8839741751642698), 'min_duration_us': np.float64(10.142), 'max_duration_us': np.float64(15.715)}]</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bf...', 'stream': 0, 'mean_duration_us': np.float64(13.91)}]</t>
         </is>
       </c>
-      <c r="T19" t="n">
+      <c r="Z19" t="n">
         <v>2.291140241269046</v>
       </c>
-      <c r="U19" t="n">
+      <c r="AA19" t="n">
         <v>92.83887776201169</v>
       </c>
     </row>
@@ -6660,37 +3522,55 @@
         <v>12.63371930803571</v>
       </c>
       <c r="L20" t="n">
+        <v>12.63371930803571</v>
+      </c>
+      <c r="M20" t="n">
         <v>12.828125</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
+        <v>12.828125</v>
+      </c>
+      <c r="O20" t="n">
         <v>0.9666591045204423</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
+        <v>0.9666591045204423</v>
+      </c>
+      <c r="Q20" t="n">
         <v>8.01708984375</v>
       </c>
-      <c r="O20" t="n">
+      <c r="R20" t="n">
+        <v>8.01708984375</v>
+      </c>
+      <c r="S20" t="n">
         <v>13.87109375</v>
       </c>
-      <c r="P20" t="n">
+      <c r="T20" t="n">
+        <v>13.87109375</v>
+      </c>
+      <c r="U20" t="n">
         <v>619.05224609375</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="V20" t="n">
+        <v>619.05224609375</v>
+      </c>
+      <c r="W20" t="n">
         <v>75</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4, 4&gt; &gt;(at::native::ReduceOp&lt;float, at::native::MeanOps&lt;float, float, float, float&gt;, unsigned int, float, 4, 4&gt;)', 'stream': 0, 'count': 49, 'total_duration_us': np.float64(619.053), 'mean_duration_us': np.float64(12.633734693877551), 'median_duration_us': np.float64(12.828), 'std_dev_duration_us': np.float64(0.9567734633782996), 'min_duration_us': np.float64(8.017), 'max_duration_us': np.float64(13.871)}]</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;floa...', 'stream': 0, 'mean_duration_us': np.float64(12.63)}]</t>
         </is>
       </c>
-      <c r="T20" t="n">
+      <c r="Z20" t="n">
         <v>2.081272694118042</v>
       </c>
-      <c r="U20" t="n">
+      <c r="AA20" t="n">
         <v>94.92015045612973</v>
       </c>
     </row>
@@ -6747,37 +3627,55 @@
         <v>10.77287801106771</v>
       </c>
       <c r="L21" t="n">
+        <v>10.77287801106771</v>
+      </c>
+      <c r="M21" t="n">
         <v>10.90380859375</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
+        <v>10.90380859375</v>
+      </c>
+      <c r="O21" t="n">
         <v>0.7221992437648039</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
+        <v>0.7221992437648039</v>
+      </c>
+      <c r="Q21" t="n">
         <v>8.37890625</v>
       </c>
-      <c r="O21" t="n">
+      <c r="R21" t="n">
+        <v>8.37890625</v>
+      </c>
+      <c r="S21" t="n">
         <v>11.9072265625</v>
       </c>
-      <c r="P21" t="n">
+      <c r="T21" t="n">
+        <v>11.9072265625</v>
+      </c>
+      <c r="U21" t="n">
         <v>517.09814453125</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="V21" t="n">
+        <v>517.09814453125</v>
+      </c>
+      <c r="W21" t="n">
         <v>129</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::neg_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#9}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 48, 'total_duration_us': np.float64(517.0999999999999), 'mean_duration_us': np.float64(10.772916666666665), 'median_duration_us': np.float64(10.904), 'std_dev_duration_us': np.float64(0.7146025070313955), 'min_duration_us': np.float64(8.379), 'max_duration_us': np.float64(11.907)}]</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(10.77)}]</t>
         </is>
       </c>
-      <c r="T21" t="n">
+      <c r="Z21" t="n">
         <v>1.738499868440847</v>
       </c>
-      <c r="U21" t="n">
+      <c r="AA21" t="n">
         <v>96.65865032457057</v>
       </c>
     </row>
@@ -6834,37 +3732,55 @@
         <v>14.97515869140625</v>
       </c>
       <c r="L22" t="n">
+        <v>14.97515869140625</v>
+      </c>
+      <c r="M22" t="n">
         <v>14.99365234375</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
+        <v>14.99365234375</v>
+      </c>
+      <c r="O22" t="n">
         <v>0.4748121556323812</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
+        <v>0.4748121556323812</v>
+      </c>
+      <c r="Q22" t="n">
         <v>14.0322265625</v>
       </c>
-      <c r="O22" t="n">
+      <c r="R22" t="n">
+        <v>14.0322265625</v>
+      </c>
+      <c r="S22" t="n">
         <v>15.794921875</v>
       </c>
-      <c r="P22" t="n">
+      <c r="T22" t="n">
+        <v>15.794921875</v>
+      </c>
+      <c r="U22" t="n">
         <v>359.40380859375</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="V22" t="n">
+        <v>359.40380859375</v>
+      </c>
+      <c r="W22" t="n">
         <v>194</v>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int, bool)#1})', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(359.404), 'mean_duration_us': np.float64(14.975166666666667), 'median_duration_us': np.float64(14.993500000000001), 'std_dev_duration_us': np.float64(0.464862315338878), 'min_duration_us': np.float64(14.032), 'max_duration_us': np.float64(15.795)}]</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel_manual_unroll&lt;128, 8, at::na...', 'stream': 0, 'mean_duration_us': np.float64(14.98)}]</t>
         </is>
       </c>
-      <c r="T22" t="n">
+      <c r="Z22" t="n">
         <v>1.208326660161925</v>
       </c>
-      <c r="U22" t="n">
+      <c r="AA22" t="n">
         <v>97.8669769847325</v>
       </c>
     </row>
@@ -6921,37 +3837,55 @@
         <v>4.557218590561225</v>
       </c>
       <c r="L23" t="n">
+        <v>4.557218590561225</v>
+      </c>
+      <c r="M23" t="n">
         <v>4.68896484375</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
+        <v>4.68896484375</v>
+      </c>
+      <c r="O23" t="n">
         <v>0.6582204563524422</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
+        <v>0.6582204563524422</v>
+      </c>
+      <c r="Q23" t="n">
         <v>1.60205078125</v>
       </c>
-      <c r="O23" t="n">
+      <c r="R23" t="n">
+        <v>1.60205078125</v>
+      </c>
+      <c r="S23" t="n">
         <v>5.33203125</v>
       </c>
-      <c r="P23" t="n">
+      <c r="T23" t="n">
+        <v>5.33203125</v>
+      </c>
+      <c r="U23" t="n">
         <v>223.3037109375</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="V23" t="n">
+        <v>223.3037109375</v>
+      </c>
+      <c r="W23" t="n">
         <v>76</v>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctorOnSelf_add&lt;float&gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::CUDAFunctorOnSelf_add&lt;float&gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 49, 'total_duration_us': np.float64(223.305), 'mean_duration_us': np.float64(4.557244897959184), 'median_duration_us': np.float64(4.689), 'std_dev_duration_us': np.float64(0.6514750462936834), 'min_duration_us': np.float64(1.602), 'max_duration_us': np.float64(5.332)}]</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 0, 'mean_duration_us': np.float64(4.56)}]</t>
         </is>
       </c>
-      <c r="T23" t="n">
+      <c r="Z23" t="n">
         <v>0.7507539452478844</v>
       </c>
-      <c r="U23" t="n">
+      <c r="AA23" t="n">
         <v>98.61773092998038</v>
       </c>
     </row>
@@ -7008,37 +3942,55 @@
         <v>4.396892936862245</v>
       </c>
       <c r="L24" t="n">
+        <v>4.396892936862245</v>
+      </c>
+      <c r="M24" t="n">
         <v>4.4501953125</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
+        <v>4.4501953125</v>
+      </c>
+      <c r="O24" t="n">
         <v>0.5811734917147134</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
+        <v>0.5811734917147134</v>
+      </c>
+      <c r="Q24" t="n">
         <v>1.72314453125</v>
       </c>
-      <c r="O24" t="n">
+      <c r="R24" t="n">
+        <v>1.72314453125</v>
+      </c>
+      <c r="S24" t="n">
         <v>4.93017578125</v>
       </c>
-      <c r="P24" t="n">
+      <c r="T24" t="n">
+        <v>4.93017578125</v>
+      </c>
+      <c r="U24" t="n">
         <v>215.44775390625</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="V24" t="n">
+        <v>215.44775390625</v>
+      </c>
+      <c r="W24" t="n">
         <v>77</v>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::rsqrt_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::rsqrt_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 49, 'total_duration_us': np.float64(215.44599999999997), 'mean_duration_us': np.float64(4.396857142857142), 'median_duration_us': np.float64(4.45), 'std_dev_duration_us': np.float64(0.5752471341137846), 'min_duration_us': np.float64(1.723), 'max_duration_us': np.float64(4.93)}]</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::rs...', 'stream': 0, 'mean_duration_us': np.float64(4.4)}]</t>
         </is>
       </c>
-      <c r="T24" t="n">
+      <c r="Z24" t="n">
         <v>0.7243419760506526</v>
       </c>
-      <c r="U24" t="n">
+      <c r="AA24" t="n">
         <v>99.34207290603104</v>
       </c>
     </row>
@@ -7095,37 +4047,55 @@
         <v>4.481038411458333</v>
       </c>
       <c r="L25" t="n">
+        <v>4.481038411458333</v>
+      </c>
+      <c r="M25" t="n">
         <v>4.68994140625</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
+        <v>4.68994140625</v>
+      </c>
+      <c r="O25" t="n">
         <v>0.9724400149355197</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
+        <v>0.9724400149355197</v>
+      </c>
+      <c r="Q25" t="n">
         <v>0.68115234375</v>
       </c>
-      <c r="O25" t="n">
+      <c r="R25" t="n">
+        <v>0.68115234375</v>
+      </c>
+      <c r="S25" t="n">
         <v>5.4111328125</v>
       </c>
-      <c r="P25" t="n">
+      <c r="T25" t="n">
+        <v>5.4111328125</v>
+      </c>
+      <c r="U25" t="n">
         <v>107.544921875</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="V25" t="n">
+        <v>107.544921875</v>
+      </c>
+      <c r="W25" t="n">
         <v>183</v>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;int&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;int&gt;, std::array&lt;char*, 1ul&gt;)', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(107.545), 'mean_duration_us': np.float64(4.481041666666667), 'median_duration_us': np.float64(4.69), 'std_dev_duration_us': np.float64(0.9520142890719772), 'min_duration_us': np.float64(0.681), 'max_duration_us': np.float64(5.411)}]</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Fi...', 'stream': 0, 'mean_duration_us': np.float64(4.48)}]</t>
         </is>
       </c>
-      <c r="T25" t="n">
+      <c r="Z25" t="n">
         <v>0.3615693355478085</v>
       </c>
-      <c r="U25" t="n">
+      <c r="AA25" t="n">
         <v>99.70364224157885</v>
       </c>
     </row>
@@ -7184,33 +4154,49 @@
       <c r="L26" t="n">
         <v>27.341796875</v>
       </c>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>27.341796875</v>
+      </c>
       <c r="N26" t="n">
         <v>27.341796875</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="n">
         <v>27.341796875</v>
       </c>
-      <c r="P26" t="n">
+      <c r="R26" t="n">
         <v>27.341796875</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="S26" t="n">
+        <v>27.341796875</v>
+      </c>
+      <c r="T26" t="n">
+        <v>27.341796875</v>
+      </c>
+      <c r="U26" t="n">
+        <v>27.341796875</v>
+      </c>
+      <c r="V26" t="n">
+        <v>27.341796875</v>
+      </c>
+      <c r="W26" t="n">
         <v>50</v>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>[{'name': 'Cijk_Ailk_Bljk_S_B_Bias_HA_S_SAV_UserArgs_MT16x16x128_MI16x16x1_SN_LDSB1_AFC1_AFEM1_AFEM1_ASEM1_CLR1_CADS0_DTVA0_DTVB0_EPS0_FDSI0_GRPM1_GRVWA2_GRVWB2_GSUAMB_GLS0_ISA942_IU1_K1_LBSPPA256_LBSPPB512_LBSPPM0_LPA16_LPB8_LPM0_LRVW4_LWPMn1_MIAV0_MIWT1_1_MO40_NTn1_NTA4_NTB0_NTC0_NTD4_NTM0_NEPBS16_NLCA1_NLCB1_ONLL1_PGR2_PLR1_PKA1_SIA3_SS1_SPO0_SRVW0_SSO0_SVW1_SK0_SKXCCM0_TLDS1_ULSGRO0_USL1_UIOFGRO0_USFGROn1_VSn1_VWA1_VWB1_WSGRA0_WSGRB0_WS64_WG16_4_4', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(27.342), 'mean_duration_us': np.float64(27.342), 'median_duration_us': np.float64(27.342), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(27.342), 'max_duration_us': np.float64(27.342)}]</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>[{'name': 'Cijk_Ailk_Bljk_S_B_Bias_HA_S_SAV_UserArgs_MT16x16x128_MI16x16x1_...', 'stream': 0, 'mean_duration_us': np.float64(27.34)}]</t>
         </is>
       </c>
-      <c r="T26" t="n">
+      <c r="Z26" t="n">
         <v>0.09192396215850518</v>
       </c>
-      <c r="U26" t="n">
+      <c r="AA26" t="n">
         <v>99.79556620373735</v>
       </c>
     </row>
@@ -7269,33 +4255,49 @@
       <c r="L27" t="n">
         <v>21.0078125</v>
       </c>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>21.0078125</v>
+      </c>
       <c r="N27" t="n">
         <v>21.0078125</v>
       </c>
-      <c r="O27" t="n">
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="n">
         <v>21.0078125</v>
       </c>
-      <c r="P27" t="n">
+      <c r="R27" t="n">
         <v>21.0078125</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
+        <v>21.0078125</v>
+      </c>
+      <c r="T27" t="n">
+        <v>21.0078125</v>
+      </c>
+      <c r="U27" t="n">
+        <v>21.0078125</v>
+      </c>
+      <c r="V27" t="n">
+        <v>21.0078125</v>
+      </c>
+      <c r="W27" t="n">
         <v>4</v>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c10::BFloat16, long, unsigned int, 2, 2, -2, true&gt;(at::cuda::detail::TensorInfo&lt;c10::BFloat16, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;c10::BFloat16 const, unsigned int&gt;, at::cuda::detail::TensorInfo&lt;long const, unsigned int&gt;, int, int, unsigned int, unsigned int, long)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(21.008), 'mean_duration_us': np.float64(21.008), 'median_duration_us': np.float64(21.008), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(21.008), 'max_duration_us': np.float64(21.008)}]</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::indexSelectLargeIndex&lt;c1...', 'stream': 0, 'mean_duration_us': np.float64(21.01)}]</t>
         </is>
       </c>
-      <c r="T27" t="n">
+      <c r="Z27" t="n">
         <v>0.07062891184919505</v>
       </c>
-      <c r="U27" t="n">
+      <c r="AA27" t="n">
         <v>99.86619511558655</v>
       </c>
     </row>
@@ -7355,34 +4357,52 @@
         <v>3.70751953125</v>
       </c>
       <c r="M28" t="n">
+        <v>3.70751953125</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.70751953125</v>
+      </c>
+      <c r="O28" t="n">
         <v>0.1422499969965125</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
+        <v>0.1422499969965125</v>
+      </c>
+      <c r="Q28" t="n">
         <v>3.60693359375</v>
       </c>
-      <c r="O28" t="n">
+      <c r="R28" t="n">
+        <v>3.60693359375</v>
+      </c>
+      <c r="S28" t="n">
         <v>3.80810546875</v>
       </c>
-      <c r="P28" t="n">
+      <c r="T28" t="n">
+        <v>3.80810546875</v>
+      </c>
+      <c r="U28" t="n">
         <v>7.4150390625</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="V28" t="n">
+        <v>7.4150390625</v>
+      </c>
+      <c r="W28" t="n">
         <v>58</v>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;float, float, float, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 2, 'total_duration_us': np.float64(7.415), 'mean_duration_us': np.float64(3.7075), 'median_duration_us': np.float64(3.7075), 'std_dev_duration_us': np.float64(0.10049999999999981), 'min_duration_us': np.float64(3.607), 'max_duration_us': np.float64(3.808)}]</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 0, 'mean_duration_us': np.float64(3.71)}]</t>
         </is>
       </c>
-      <c r="T28" t="n">
+      <c r="Z28" t="n">
         <v>0.02492958942315629</v>
       </c>
-      <c r="U28" t="n">
+      <c r="AA28" t="n">
         <v>99.8911247050097</v>
       </c>
     </row>
@@ -7441,33 +4461,49 @@
       <c r="L29" t="n">
         <v>6.3330078125</v>
       </c>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>6.3330078125</v>
+      </c>
       <c r="N29" t="n">
         <v>6.3330078125</v>
       </c>
-      <c r="O29" t="n">
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="n">
         <v>6.3330078125</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
         <v>6.3330078125</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="S29" t="n">
+        <v>6.3330078125</v>
+      </c>
+      <c r="T29" t="n">
+        <v>6.3330078125</v>
+      </c>
+      <c r="U29" t="n">
+        <v>6.3330078125</v>
+      </c>
+      <c r="V29" t="n">
+        <v>6.3330078125</v>
+      </c>
+      <c r="W29" t="n">
         <v>55</v>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;4u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(6.333), 'mean_duration_us': np.float64(6.333), 'median_duration_us': np.float64(6.333), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(6.333), 'max_duration_us': np.float64(6.333)}]</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::...', 'stream': 0, 'mean_duration_us': np.float64(6.33)}]</t>
         </is>
       </c>
-      <c r="T29" t="n">
+      <c r="Z29" t="n">
         <v>0.02129176707614494</v>
       </c>
-      <c r="U29" t="n">
+      <c r="AA29" t="n">
         <v>99.91241647208585</v>
       </c>
     </row>
@@ -7526,33 +4562,49 @@
       <c r="L30" t="n">
         <v>5.57177734375</v>
       </c>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>5.57177734375</v>
+      </c>
       <c r="N30" t="n">
         <v>5.57177734375</v>
       </c>
-      <c r="O30" t="n">
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="n">
         <v>5.57177734375</v>
       </c>
-      <c r="P30" t="n">
+      <c r="R30" t="n">
         <v>5.57177734375</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="S30" t="n">
+        <v>5.57177734375</v>
+      </c>
+      <c r="T30" t="n">
+        <v>5.57177734375</v>
+      </c>
+      <c r="U30" t="n">
+        <v>5.57177734375</v>
+      </c>
+      <c r="V30" t="n">
+        <v>5.57177734375</v>
+      </c>
+      <c r="W30" t="n">
         <v>14</v>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;long, long, bool, at::native::(anonymous namespace)::CompareEqFunctor&lt;long&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(5.572), 'mean_duration_us': np.float64(5.572), 'median_duration_us': np.float64(5.572), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(5.572), 'max_duration_us': np.float64(5.572)}]</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 0, 'mean_duration_us': np.float64(5.57)}]</t>
         </is>
       </c>
-      <c r="T30" t="n">
+      <c r="Z30" t="n">
         <v>0.01873248682389282</v>
       </c>
-      <c r="U30" t="n">
+      <c r="AA30" t="n">
         <v>99.93114895890974</v>
       </c>
     </row>
@@ -7611,33 +4663,49 @@
       <c r="L31" t="n">
         <v>4.68994140625</v>
       </c>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>4.68994140625</v>
+      </c>
       <c r="N31" t="n">
         <v>4.68994140625</v>
       </c>
-      <c r="O31" t="n">
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="n">
         <v>4.68994140625</v>
       </c>
-      <c r="P31" t="n">
+      <c r="R31" t="n">
         <v>4.68994140625</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="S31" t="n">
+        <v>4.68994140625</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4.68994140625</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4.68994140625</v>
+      </c>
+      <c r="V31" t="n">
+        <v>4.68994140625</v>
+      </c>
+      <c r="W31" t="n">
         <v>56</v>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::cos_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::cos_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(4.69), 'mean_duration_us': np.float64(4.69), 'median_duration_us': np.float64(4.69), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(4.69), 'max_duration_us': np.float64(4.69)}]</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::co...', 'stream': 0, 'mean_duration_us': np.float64(4.69)}]</t>
         </is>
       </c>
-      <c r="T31" t="n">
+      <c r="Z31" t="n">
         <v>0.01576772727574188</v>
       </c>
-      <c r="U31" t="n">
+      <c r="AA31" t="n">
         <v>99.94691668618549</v>
       </c>
     </row>
@@ -7696,33 +4764,49 @@
       <c r="L32" t="n">
         <v>4.2490234375</v>
       </c>
-      <c r="M32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>4.2490234375</v>
+      </c>
       <c r="N32" t="n">
         <v>4.2490234375</v>
       </c>
-      <c r="O32" t="n">
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="n">
         <v>4.2490234375</v>
       </c>
-      <c r="P32" t="n">
+      <c r="R32" t="n">
         <v>4.2490234375</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="S32" t="n">
+        <v>4.2490234375</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4.2490234375</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4.2490234375</v>
+      </c>
+      <c r="V32" t="n">
+        <v>4.2490234375</v>
+      </c>
+      <c r="W32" t="n">
         <v>57</v>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::sin_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::sin_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#2}::operator()() const::{lambda()#2}::operator()() const::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(4.249), 'mean_duration_us': np.float64(4.249), 'median_duration_us': np.float64(4.249), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(4.249), 'max_duration_us': np.float64(4.249)}]</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::si...', 'stream': 0, 'mean_duration_us': np.float64(4.25)}]</t>
         </is>
       </c>
-      <c r="T32" t="n">
+      <c r="Z32" t="n">
         <v>0.0142853475016664</v>
       </c>
-      <c r="U32" t="n">
+      <c r="AA32" t="n">
         <v>99.96120203368716</v>
       </c>
     </row>
@@ -7781,33 +4865,49 @@
       <c r="L33" t="n">
         <v>3.0859375</v>
       </c>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>3.0859375</v>
+      </c>
       <c r="N33" t="n">
         <v>3.0859375</v>
       </c>
-      <c r="O33" t="n">
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="n">
         <v>3.0859375</v>
       </c>
-      <c r="P33" t="n">
+      <c r="R33" t="n">
         <v>3.0859375</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="S33" t="n">
+        <v>3.0859375</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3.0859375</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3.0859375</v>
+      </c>
+      <c r="V33" t="n">
+        <v>3.0859375</v>
+      </c>
+      <c r="W33" t="n">
         <v>38</v>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#7}::operator()() const::{lambda(float)#1} const&amp;)::{lambda(int)#1})', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(3.086), 'mean_duration_us': np.float64(3.086), 'median_duration_us': np.float64(3.086), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.086), 'max_duration_us': np.float64(3.086)}]</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::elementwise_kernel&lt;512, 1, at::native::gpu_kern...', 'stream': 0, 'mean_duration_us': np.float64(3.09)}]</t>
         </is>
       </c>
-      <c r="T33" t="n">
+      <c r="Z33" t="n">
         <v>0.01037501680194572</v>
       </c>
-      <c r="U33" t="n">
+      <c r="AA33" t="n">
         <v>99.9715770504891</v>
       </c>
     </row>
@@ -7867,34 +4967,52 @@
         <v>1.54248046875</v>
       </c>
       <c r="M34" t="n">
+        <v>1.54248046875</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1.54248046875</v>
+      </c>
+      <c r="O34" t="n">
         <v>0.02900242657210449</v>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
+        <v>0.02900242657210449</v>
+      </c>
+      <c r="Q34" t="n">
         <v>1.52197265625</v>
       </c>
-      <c r="O34" t="n">
+      <c r="R34" t="n">
+        <v>1.52197265625</v>
+      </c>
+      <c r="S34" t="n">
         <v>1.56298828125</v>
       </c>
-      <c r="P34" t="n">
+      <c r="T34" t="n">
+        <v>1.56298828125</v>
+      </c>
+      <c r="U34" t="n">
         <v>3.0849609375</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="V34" t="n">
+        <v>3.0849609375</v>
+      </c>
+      <c r="W34" t="n">
         <v>63</v>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::bfloat16_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda(float)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 0, 'count': 2, 'total_duration_us': np.float64(3.085), 'mean_duration_us': np.float64(1.5425), 'median_duration_us': np.float64(1.5425), 'std_dev_duration_us': np.float64(0.020499999999999963), 'min_duration_us': np.float64(1.522), 'max_duration_us': np.float64(1.563)}]</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::bf...', 'stream': 0, 'mean_duration_us': np.float64(1.54)}]</t>
         </is>
       </c>
-      <c r="T34" t="n">
+      <c r="Z34" t="n">
         <v>0.01037173356878055</v>
       </c>
-      <c r="U34" t="n">
+      <c r="AA34" t="n">
         <v>99.98194878405788</v>
       </c>
     </row>
@@ -7953,33 +5071,49 @@
       <c r="L35" t="n">
         <v>2.3251953125</v>
       </c>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="n">
+        <v>2.3251953125</v>
+      </c>
       <c r="N35" t="n">
         <v>2.3251953125</v>
       </c>
-      <c r="O35" t="n">
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="n">
         <v>2.3251953125</v>
       </c>
-      <c r="P35" t="n">
+      <c r="R35" t="n">
         <v>2.3251953125</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="S35" t="n">
+        <v>2.3251953125</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.3251953125</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2.3251953125</v>
+      </c>
+      <c r="V35" t="n">
+        <v>2.3251953125</v>
+      </c>
+      <c r="W35" t="n">
         <v>15</v>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;bool, at::native::func_wrapper_t&lt;bool, at::native::and_kernel_cuda(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, bool)#1}&gt;, unsigned int, bool, 4, 4&gt; &gt;(at::native::ReduceOp&lt;bool, at::native::func_wrapper_t&lt;bool, at::native::and_kernel_cuda(at::TensorIterator&amp;)::{lambda()#1}::operator()() const::{lambda()#12}::operator()() const::{lambda(bool, bool)#1}&gt;, unsigned int, bool, 4, 4&gt;)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(2.325), 'mean_duration_us': np.float64(2.325), 'median_duration_us': np.float64(2.325), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.325), 'max_duration_us': np.float64(2.325)}]</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>[{'name': 'void at::native::reduce_kernel&lt;512, 1, at::native::ReduceOp&lt;bool...', 'stream': 0, 'mean_duration_us': np.float64(2.33)}]</t>
         </is>
       </c>
-      <c r="T35" t="n">
+      <c r="Z35" t="n">
         <v>0.007817378166276191</v>
       </c>
-      <c r="U35" t="n">
+      <c r="AA35" t="n">
         <v>99.98976616222416</v>
       </c>
     </row>
@@ -8038,33 +5172,49 @@
       <c r="L36" t="n">
         <v>2.2841796875</v>
       </c>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" t="n">
+        <v>2.2841796875</v>
+      </c>
       <c r="N36" t="n">
         <v>2.2841796875</v>
       </c>
-      <c r="O36" t="n">
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="n">
         <v>2.2841796875</v>
       </c>
-      <c r="P36" t="n">
+      <c r="R36" t="n">
         <v>2.2841796875</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="S36" t="n">
+        <v>2.2841796875</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.2841796875</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.2841796875</v>
+      </c>
+      <c r="V36" t="n">
+        <v>2.2841796875</v>
+      </c>
+      <c r="W36" t="n">
         <v>10</v>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;(int, at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}, function_traits&lt;at::native::arange_cuda_out(c10::Scalar const&amp;, c10::Scalar const&amp;, c10::Scalar const&amp;, at::Tensor&amp;)::{lambda()#1}::operator()() const::{lambda()#4}::operator()() const::{lambda(long)#1}&gt;::result_type*)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(2.284), 'mean_duration_us': np.float64(2.284), 'median_duration_us': np.float64(2.284), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.284), 'max_duration_us': np.float64(2.284)}]</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>[{'name': 'void (anonymous namespace)::elementwise_kernel_with_index&lt;int, a...', 'stream': 0, 'mean_duration_us': np.float64(2.28)}]</t>
         </is>
       </c>
-      <c r="T36" t="n">
+      <c r="Z36" t="n">
         <v>0.007679482373338938</v>
       </c>
-      <c r="U36" t="n">
+      <c r="AA36" t="n">
         <v>99.99744564459749</v>
       </c>
     </row>
@@ -8123,33 +5273,49 @@
       <c r="L37" t="n">
         <v>0.759765625</v>
       </c>
-      <c r="M37" t="inlineStr"/>
+      <c r="M37" t="n">
+        <v>0.759765625</v>
+      </c>
       <c r="N37" t="n">
         <v>0.759765625</v>
       </c>
-      <c r="O37" t="n">
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="n">
         <v>0.759765625</v>
       </c>
-      <c r="P37" t="n">
+      <c r="R37" t="n">
         <v>0.759765625</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="S37" t="n">
+        <v>0.759765625</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.759765625</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.759765625</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.759765625</v>
+      </c>
+      <c r="W37" t="n">
         <v>19</v>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 0, 'count': 1, 'total_duration_us': np.float64(0.76), 'mean_duration_us': np.float64(0.76), 'median_duration_us': np.float64(0.76), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(0.76), 'max_duration_us': np.float64(0.76)}]</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>[{'name': 'Memcpy DtoD (Device -&gt; Device)', 'stream': 0, 'mean_duration_us': np.float64(0.76)}]</t>
         </is>
       </c>
-      <c r="T37" t="n">
+      <c r="Z37" t="n">
         <v>0.002554355402504358</v>
       </c>
-      <c r="U37" t="n">
+      <c r="AA37" t="n">
         <v>100</v>
       </c>
     </row>
@@ -8671,12 +5837,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;int&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;int&gt;, std::array&lt;char*, 1ul&gt;)', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(107.545), 'mean_duration_us': np.float64(4.481041666666667), 'median_duration_us': np.float64(4.69), 'std_dev_duration_us': np.float64(0.9520142890719772), 'min_duration_us': np.float64(0.681), 'max_duration_us': np.float64(5.411)}, {'name': 'attn_fwd', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(3908.798), 'mean_duration_us': np.float64(162.86658333333332), 'median_duration_us': np.float64(164.23700000000002), 'std_dev_duration_us': np.float64(9.253315184825505), 'min_duration_us': np.float64(138.557), 'max_duration_us': np.float64(173.077)}]</t>
+          <t>[{'name': 'attn_fwd', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(3908.798), 'mean_duration_us': np.float64(162.86658333333332), 'median_duration_us': np.float64(164.23700000000002), 'std_dev_duration_us': np.float64(9.253315184825505), 'min_duration_us': np.float64(138.557), 'max_duration_us': np.float64(173.077)}, {'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::FillFunctor&lt;int&gt;, std::array&lt;char*, 1ul&gt; &gt;(int, at::native::FillFunctor&lt;int&gt;, std::array&lt;char*, 1ul&gt;)', 'stream': 0, 'count': 24, 'total_duration_us': np.float64(107.545), 'mean_duration_us': np.float64(4.481041666666667), 'median_duration_us': np.float64(4.69), 'std_dev_duration_us': np.float64(0.9520142890719772), 'min_duration_us': np.float64(0.681), 'max_duration_us': np.float64(5.411)}]</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Fi...', 'stream': 0, 'mean_duration_us': np.float64(4.48)}, {'name': 'attn_fwd', 'stream': 0, 'mean_duration_us': np.float64(162.87)}]</t>
+          <t>[{'name': 'attn_fwd', 'stream': 0, 'mean_duration_us': np.float64(162.87)}, {'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::Fi...', 'stream': 0, 'mean_duration_us': np.float64(4.48)}]</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
